--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 днрсч ост ки от Титенко.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 днрсч ост ки от Титенко.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\29,06,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA138775-9AFC-4D96-93FA-A1157205BE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593BB8F8-9997-4AC4-B35E-2955470D9B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA499"/>
+  <dimension ref="A1:AZ499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -942,12 +942,11 @@
     <col min="26" max="30" width="6" customWidth="1"/>
     <col min="31" max="31" width="29.7109375" customWidth="1"/>
     <col min="32" max="33" width="7" customWidth="1"/>
-    <col min="34" max="34" width="5" customWidth="1"/>
-    <col min="35" max="35" width="6.5703125" customWidth="1"/>
-    <col min="36" max="53" width="5" customWidth="1"/>
+    <col min="34" max="34" width="6.5703125" customWidth="1"/>
+    <col min="35" max="52" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1000,9 +999,8 @@
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-    </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1055,9 +1053,8 @@
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
-      <c r="BA2" s="1"/>
-    </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1176,9 +1173,8 @@
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
       <c r="AZ3" s="1"/>
-      <c r="BA3" s="1"/>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1255,9 +1251,8 @@
       <c r="AX4" s="1"/>
       <c r="AY4" s="1"/>
       <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1354,11 +1349,11 @@
         <f>SUM(AG6:AG499)</f>
         <v>4309.130000000001</v>
       </c>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="4">
-        <f>SUM(AI6:AI499)</f>
+      <c r="AH5" s="4">
+        <f>SUM(AH6:AH499)</f>
         <v>1898.9342300000005</v>
       </c>
+      <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
@@ -1376,9 +1371,8 @@
       <c r="AX5" s="1"/>
       <c r="AY5" s="1"/>
       <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-    </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -1474,11 +1468,11 @@
         <f>G6*U6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1">
+      <c r="AH6" s="1">
         <f>Q6*G6</f>
         <v>20</v>
       </c>
+      <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
@@ -1496,9 +1490,8 @@
       <c r="AX6" s="1"/>
       <c r="AY6" s="1"/>
       <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-    </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1590,11 +1583,11 @@
         <f t="shared" ref="AG7:AG70" si="8">G7*U7</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1">
-        <f t="shared" ref="AI7:AI70" si="9">Q7*G7</f>
+      <c r="AH7" s="1">
+        <f t="shared" ref="AH7:AH70" si="9">Q7*G7</f>
         <v>1.204</v>
       </c>
+      <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
@@ -1612,9 +1605,8 @@
       <c r="AX7" s="1"/>
       <c r="AY7" s="1"/>
       <c r="AZ7" s="1"/>
-      <c r="BA7" s="1"/>
-    </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1708,11 +1700,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1">
+      <c r="AH8" s="1">
         <f t="shared" si="9"/>
         <v>6.75</v>
       </c>
+      <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
@@ -1730,9 +1722,8 @@
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-    </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -1770,10 +1761,10 @@
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="1">
+      <c r="O9" s="16">
         <v>800</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="16">
         <v>500</v>
       </c>
       <c r="Q9" s="1">
@@ -1832,11 +1823,11 @@
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1">
+      <c r="AH9" s="1">
         <f t="shared" si="9"/>
         <v>210.96819999999997</v>
       </c>
+      <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
@@ -1854,9 +1845,8 @@
       <c r="AX9" s="1"/>
       <c r="AY9" s="1"/>
       <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-    </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -1950,11 +1940,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1">
+      <c r="AH10" s="1">
         <f t="shared" si="9"/>
         <v>1.2092000000000001</v>
       </c>
+      <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
@@ -1972,9 +1962,8 @@
       <c r="AX10" s="1"/>
       <c r="AY10" s="1"/>
       <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-    </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
@@ -2012,10 +2001,10 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="1">
+      <c r="O11" s="16">
         <v>90</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="16">
         <v>90</v>
       </c>
       <c r="Q11" s="1">
@@ -2072,11 +2061,11 @@
         <f t="shared" si="8"/>
         <v>122</v>
       </c>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1">
+      <c r="AH11" s="1">
         <f t="shared" si="9"/>
         <v>35.412799999999997</v>
       </c>
+      <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
@@ -2094,9 +2083,8 @@
       <c r="AX11" s="1"/>
       <c r="AY11" s="1"/>
       <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -2137,7 +2125,7 @@
       <c r="O12" s="1">
         <v>290</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="16">
         <v>290</v>
       </c>
       <c r="Q12" s="1">
@@ -2194,11 +2182,11 @@
         <f t="shared" si="8"/>
         <v>255</v>
       </c>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1">
+      <c r="AH12" s="1">
         <f t="shared" si="9"/>
         <v>97.275999999999996</v>
       </c>
+      <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
@@ -2216,9 +2204,8 @@
       <c r="AX12" s="1"/>
       <c r="AY12" s="1"/>
       <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-    </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -2315,11 +2302,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH13" s="1"/>
-      <c r="AI13" s="1">
+      <c r="AH13" s="1">
         <f t="shared" si="9"/>
         <v>4.3499999999999996</v>
       </c>
+      <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
@@ -2337,9 +2324,8 @@
       <c r="AX13" s="1"/>
       <c r="AY13" s="1"/>
       <c r="AZ13" s="1"/>
-      <c r="BA13" s="1"/>
-    </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -2437,11 +2423,11 @@
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
-      <c r="AH14" s="1"/>
-      <c r="AI14" s="1">
+      <c r="AH14" s="1">
         <f t="shared" si="9"/>
         <v>15.771799999999999</v>
       </c>
+      <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
@@ -2459,9 +2445,8 @@
       <c r="AX14" s="1"/>
       <c r="AY14" s="1"/>
       <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-    </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -2553,11 +2538,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1">
+      <c r="AH15" s="1">
         <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
+      <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
@@ -2575,9 +2560,8 @@
       <c r="AX15" s="1"/>
       <c r="AY15" s="1"/>
       <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-    </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -2676,11 +2660,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1">
+      <c r="AH16" s="1">
         <f t="shared" si="9"/>
         <v>33.44</v>
       </c>
+      <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
@@ -2698,9 +2682,8 @@
       <c r="AX16" s="1"/>
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-    </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -2800,11 +2783,11 @@
         <f t="shared" si="8"/>
         <v>176</v>
       </c>
-      <c r="AH17" s="1"/>
-      <c r="AI17" s="1">
+      <c r="AH17" s="1">
         <f t="shared" si="9"/>
         <v>60.511800000000008</v>
       </c>
+      <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
@@ -2822,9 +2805,8 @@
       <c r="AX17" s="1"/>
       <c r="AY17" s="1"/>
       <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-    </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -2919,11 +2901,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1">
+      <c r="AH18" s="1">
         <f t="shared" si="9"/>
         <v>2.4303999999999997</v>
       </c>
+      <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
@@ -2941,9 +2923,8 @@
       <c r="AX18" s="1"/>
       <c r="AY18" s="1"/>
       <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-    </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
@@ -3043,11 +3024,11 @@
         <f t="shared" si="8"/>
         <v>86.4</v>
       </c>
-      <c r="AH19" s="1"/>
-      <c r="AI19" s="1">
+      <c r="AH19" s="1">
         <f t="shared" si="9"/>
         <v>21.840000000000003</v>
       </c>
+      <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
@@ -3065,9 +3046,8 @@
       <c r="AX19" s="1"/>
       <c r="AY19" s="1"/>
       <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-    </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -3161,11 +3141,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="1"/>
-      <c r="AI20" s="1">
+      <c r="AH20" s="1">
         <f t="shared" si="9"/>
         <v>43.7378</v>
       </c>
+      <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
@@ -3183,9 +3163,8 @@
       <c r="AX20" s="1"/>
       <c r="AY20" s="1"/>
       <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-    </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -3282,11 +3261,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="1"/>
-      <c r="AI21" s="1">
+      <c r="AH21" s="1">
         <f t="shared" si="9"/>
         <v>7.6559999999999997</v>
       </c>
+      <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
@@ -3304,9 +3283,8 @@
       <c r="AX21" s="1"/>
       <c r="AY21" s="1"/>
       <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-    </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -3388,11 +3366,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="1"/>
-      <c r="AI22" s="1">
+      <c r="AH22" s="1">
         <f t="shared" si="9"/>
         <v>8.4480000000000004</v>
       </c>
+      <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
@@ -3410,9 +3388,8 @@
       <c r="AX22" s="1"/>
       <c r="AY22" s="1"/>
       <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-    </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>53</v>
       </c>
@@ -3509,11 +3486,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="1"/>
-      <c r="AI23" s="1">
+      <c r="AH23" s="1">
         <f t="shared" si="9"/>
         <v>0.56999999999999995</v>
       </c>
+      <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
@@ -3531,9 +3508,8 @@
       <c r="AX23" s="1"/>
       <c r="AY23" s="1"/>
       <c r="AZ23" s="1"/>
-      <c r="BA23" s="1"/>
-    </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>55</v>
       </c>
@@ -3635,11 +3611,11 @@
         <f t="shared" si="8"/>
         <v>71</v>
       </c>
-      <c r="AH24" s="1"/>
-      <c r="AI24" s="1">
+      <c r="AH24" s="1">
         <f t="shared" si="9"/>
         <v>53.355600000000003</v>
       </c>
+      <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
@@ -3657,9 +3633,8 @@
       <c r="AX24" s="1"/>
       <c r="AY24" s="1"/>
       <c r="AZ24" s="1"/>
-      <c r="BA24" s="1"/>
-    </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -3757,11 +3732,11 @@
         <f t="shared" si="8"/>
         <v>17.82</v>
       </c>
-      <c r="AH25" s="1"/>
-      <c r="AI25" s="1">
+      <c r="AH25" s="1">
         <f t="shared" si="9"/>
         <v>7.47</v>
       </c>
+      <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
@@ -3779,9 +3754,8 @@
       <c r="AX25" s="1"/>
       <c r="AY25" s="1"/>
       <c r="AZ25" s="1"/>
-      <c r="BA25" s="1"/>
-    </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>58</v>
       </c>
@@ -3875,11 +3849,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="1"/>
-      <c r="AI26" s="1">
+      <c r="AH26" s="1">
         <f t="shared" si="9"/>
         <v>0.89999999999999991</v>
       </c>
+      <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
@@ -3897,9 +3871,8 @@
       <c r="AX26" s="1"/>
       <c r="AY26" s="1"/>
       <c r="AZ26" s="1"/>
-      <c r="BA26" s="1"/>
-    </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -3991,11 +3964,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="1"/>
-      <c r="AI27" s="1">
+      <c r="AH27" s="1">
         <f t="shared" si="9"/>
         <v>2.04</v>
       </c>
+      <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
@@ -4013,9 +3986,8 @@
       <c r="AX27" s="1"/>
       <c r="AY27" s="1"/>
       <c r="AZ27" s="1"/>
-      <c r="BA27" s="1"/>
-    </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -4109,11 +4081,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="1"/>
-      <c r="AI28" s="1">
+      <c r="AH28" s="1">
         <f t="shared" si="9"/>
         <v>42.266199999999998</v>
       </c>
+      <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
@@ -4131,9 +4103,8 @@
       <c r="AX28" s="1"/>
       <c r="AY28" s="1"/>
       <c r="AZ28" s="1"/>
-      <c r="BA28" s="1"/>
-    </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>61</v>
       </c>
@@ -4223,11 +4194,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="1"/>
-      <c r="AI29" s="1">
+      <c r="AH29" s="1">
         <f t="shared" si="9"/>
         <v>-0.16000000000000003</v>
       </c>
+      <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
@@ -4245,9 +4216,8 @@
       <c r="AX29" s="1"/>
       <c r="AY29" s="1"/>
       <c r="AZ29" s="1"/>
-      <c r="BA29" s="1"/>
-    </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>63</v>
       </c>
@@ -4344,11 +4314,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="1"/>
-      <c r="AI30" s="1">
+      <c r="AH30" s="1">
         <f t="shared" si="9"/>
         <v>2.8000000000000003</v>
       </c>
+      <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
@@ -4366,9 +4336,8 @@
       <c r="AX30" s="1"/>
       <c r="AY30" s="1"/>
       <c r="AZ30" s="1"/>
-      <c r="BA30" s="1"/>
-    </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
@@ -4468,11 +4437,11 @@
         <f t="shared" si="8"/>
         <v>287.60000000000002</v>
       </c>
-      <c r="AH31" s="1"/>
-      <c r="AI31" s="1">
+      <c r="AH31" s="1">
         <f t="shared" si="9"/>
         <v>53.84</v>
       </c>
+      <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
@@ -4490,9 +4459,8 @@
       <c r="AX31" s="1"/>
       <c r="AY31" s="1"/>
       <c r="AZ31" s="1"/>
-      <c r="BA31" s="1"/>
-    </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,11 +4560,11 @@
         <f t="shared" si="8"/>
         <v>139.20000000000002</v>
       </c>
-      <c r="AH32" s="1"/>
-      <c r="AI32" s="1">
+      <c r="AH32" s="1">
         <f t="shared" si="9"/>
         <v>22.96</v>
       </c>
+      <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
@@ -4614,9 +4582,8 @@
       <c r="AX32" s="1"/>
       <c r="AY32" s="1"/>
       <c r="AZ32" s="1"/>
-      <c r="BA32" s="1"/>
-    </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
@@ -4716,11 +4683,11 @@
         <f t="shared" si="8"/>
         <v>176.4</v>
       </c>
-      <c r="AH33" s="1"/>
-      <c r="AI33" s="1">
+      <c r="AH33" s="1">
         <f t="shared" si="9"/>
         <v>53.576000000000001</v>
       </c>
+      <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
@@ -4738,9 +4705,8 @@
       <c r="AX33" s="1"/>
       <c r="AY33" s="1"/>
       <c r="AZ33" s="1"/>
-      <c r="BA33" s="1"/>
-    </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -4840,11 +4806,11 @@
         <f t="shared" si="8"/>
         <v>8.9</v>
       </c>
-      <c r="AH34" s="1"/>
-      <c r="AI34" s="1">
+      <c r="AH34" s="1">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
+      <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
@@ -4862,9 +4828,8 @@
       <c r="AX34" s="1"/>
       <c r="AY34" s="1"/>
       <c r="AZ34" s="1"/>
-      <c r="BA34" s="1"/>
-    </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
@@ -4964,11 +4929,11 @@
         <f t="shared" si="8"/>
         <v>20.700000000000003</v>
       </c>
-      <c r="AH35" s="1"/>
-      <c r="AI35" s="1">
+      <c r="AH35" s="1">
         <f t="shared" si="9"/>
         <v>4.12</v>
       </c>
+      <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
@@ -4986,9 +4951,8 @@
       <c r="AX35" s="1"/>
       <c r="AY35" s="1"/>
       <c r="AZ35" s="1"/>
-      <c r="BA35" s="1"/>
-    </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>69</v>
       </c>
@@ -5083,11 +5047,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="1"/>
-      <c r="AI36" s="1">
+      <c r="AH36" s="1">
         <f t="shared" si="9"/>
         <v>2.12</v>
       </c>
+      <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
@@ -5105,9 +5069,8 @@
       <c r="AX36" s="1"/>
       <c r="AY36" s="1"/>
       <c r="AZ36" s="1"/>
-      <c r="BA36" s="1"/>
-    </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>70</v>
       </c>
@@ -5193,11 +5156,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="1"/>
-      <c r="AI37" s="1">
+      <c r="AH37" s="1">
         <f t="shared" si="9"/>
         <v>2.4239999999999999</v>
       </c>
+      <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
@@ -5215,9 +5178,8 @@
       <c r="AX37" s="1"/>
       <c r="AY37" s="1"/>
       <c r="AZ37" s="1"/>
-      <c r="BA37" s="1"/>
-    </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>71</v>
       </c>
@@ -5312,11 +5274,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="1"/>
-      <c r="AI38" s="1">
+      <c r="AH38" s="1">
         <f t="shared" si="9"/>
         <v>4.24</v>
       </c>
+      <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
@@ -5334,9 +5296,8 @@
       <c r="AX38" s="1"/>
       <c r="AY38" s="1"/>
       <c r="AZ38" s="1"/>
-      <c r="BA38" s="1"/>
-    </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>72</v>
       </c>
@@ -5428,11 +5389,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="1"/>
-      <c r="AI39" s="1">
+      <c r="AH39" s="1">
         <f t="shared" si="9"/>
         <v>8.76</v>
       </c>
+      <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
@@ -5450,9 +5411,8 @@
       <c r="AX39" s="1"/>
       <c r="AY39" s="1"/>
       <c r="AZ39" s="1"/>
-      <c r="BA39" s="1"/>
-    </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>73</v>
       </c>
@@ -5550,11 +5510,11 @@
         <f t="shared" si="8"/>
         <v>92</v>
       </c>
-      <c r="AH40" s="1"/>
-      <c r="AI40" s="1">
+      <c r="AH40" s="1">
         <f t="shared" si="9"/>
         <v>21.777200000000001</v>
       </c>
+      <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
@@ -5572,9 +5532,8 @@
       <c r="AX40" s="1"/>
       <c r="AY40" s="1"/>
       <c r="AZ40" s="1"/>
-      <c r="BA40" s="1"/>
-    </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>74</v>
       </c>
@@ -5671,11 +5630,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="1"/>
-      <c r="AI41" s="1">
+      <c r="AH41" s="1">
         <f t="shared" si="9"/>
         <v>11.2448</v>
       </c>
+      <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
@@ -5693,9 +5652,8 @@
       <c r="AX41" s="1"/>
       <c r="AY41" s="1"/>
       <c r="AZ41" s="1"/>
-      <c r="BA41" s="1"/>
-    </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>75</v>
       </c>
@@ -5793,11 +5751,11 @@
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
-      <c r="AH42" s="1"/>
-      <c r="AI42" s="1">
+      <c r="AH42" s="1">
         <f t="shared" si="9"/>
         <v>22.173999999999999</v>
       </c>
+      <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
@@ -5815,9 +5773,8 @@
       <c r="AX42" s="1"/>
       <c r="AY42" s="1"/>
       <c r="AZ42" s="1"/>
-      <c r="BA42" s="1"/>
-    </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>76</v>
       </c>
@@ -5915,11 +5872,11 @@
         <f t="shared" si="8"/>
         <v>131</v>
       </c>
-      <c r="AH43" s="1"/>
-      <c r="AI43" s="1">
+      <c r="AH43" s="1">
         <f t="shared" si="9"/>
         <v>38.509399999999999</v>
       </c>
+      <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
@@ -5937,9 +5894,8 @@
       <c r="AX43" s="1"/>
       <c r="AY43" s="1"/>
       <c r="AZ43" s="1"/>
-      <c r="BA43" s="1"/>
-    </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
@@ -6033,11 +5989,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH44" s="1"/>
-      <c r="AI44" s="1">
+      <c r="AH44" s="1">
         <f t="shared" si="9"/>
         <v>141.78</v>
       </c>
+      <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
@@ -6055,9 +6011,8 @@
       <c r="AX44" s="1"/>
       <c r="AY44" s="1"/>
       <c r="AZ44" s="1"/>
-      <c r="BA44" s="1"/>
-    </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>78</v>
       </c>
@@ -6152,11 +6107,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="1"/>
-      <c r="AI45" s="1">
+      <c r="AH45" s="1">
         <f t="shared" si="9"/>
         <v>2.1646000000000001</v>
       </c>
+      <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
@@ -6174,9 +6129,8 @@
       <c r="AX45" s="1"/>
       <c r="AY45" s="1"/>
       <c r="AZ45" s="1"/>
-      <c r="BA45" s="1"/>
-    </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>79</v>
       </c>
@@ -6214,7 +6168,7 @@
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-      <c r="O46" s="1">
+      <c r="O46" s="16">
         <v>900</v>
       </c>
       <c r="P46" s="1">
@@ -6276,11 +6230,11 @@
         <f t="shared" si="8"/>
         <v>146.64999999999998</v>
       </c>
-      <c r="AH46" s="1"/>
-      <c r="AI46" s="1">
+      <c r="AH46" s="1">
         <f t="shared" si="9"/>
         <v>75.53</v>
       </c>
+      <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
@@ -6298,9 +6252,8 @@
       <c r="AX46" s="1"/>
       <c r="AY46" s="1"/>
       <c r="AZ46" s="1"/>
-      <c r="BA46" s="1"/>
-    </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>80</v>
       </c>
@@ -6400,11 +6353,11 @@
         <f t="shared" si="8"/>
         <v>174.25</v>
       </c>
-      <c r="AH47" s="1"/>
-      <c r="AI47" s="1">
+      <c r="AH47" s="1">
         <f t="shared" si="9"/>
         <v>35.014000000000003</v>
       </c>
+      <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
@@ -6422,9 +6375,8 @@
       <c r="AX47" s="1"/>
       <c r="AY47" s="1"/>
       <c r="AZ47" s="1"/>
-      <c r="BA47" s="1"/>
-    </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>81</v>
       </c>
@@ -6516,11 +6468,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH48" s="1"/>
-      <c r="AI48" s="1">
+      <c r="AH48" s="1">
         <f t="shared" si="9"/>
         <v>5.1659999999999995</v>
       </c>
+      <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
@@ -6538,9 +6490,8 @@
       <c r="AX48" s="1"/>
       <c r="AY48" s="1"/>
       <c r="AZ48" s="1"/>
-      <c r="BA48" s="1"/>
-    </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>82</v>
       </c>
@@ -6640,11 +6591,11 @@
         <f t="shared" si="8"/>
         <v>29.16</v>
       </c>
-      <c r="AH49" s="1"/>
-      <c r="AI49" s="1">
+      <c r="AH49" s="1">
         <f t="shared" si="9"/>
         <v>15.336</v>
       </c>
+      <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
@@ -6662,9 +6613,8 @@
       <c r="AX49" s="1"/>
       <c r="AY49" s="1"/>
       <c r="AZ49" s="1"/>
-      <c r="BA49" s="1"/>
-    </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>83</v>
       </c>
@@ -6764,11 +6714,11 @@
         <f t="shared" si="8"/>
         <v>91.410000000000011</v>
       </c>
-      <c r="AH50" s="1"/>
-      <c r="AI50" s="1">
+      <c r="AH50" s="1">
         <f t="shared" si="9"/>
         <v>18.612000000000002</v>
       </c>
+      <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
@@ -6786,9 +6736,8 @@
       <c r="AX50" s="1"/>
       <c r="AY50" s="1"/>
       <c r="AZ50" s="1"/>
-      <c r="BA50" s="1"/>
-    </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>84</v>
       </c>
@@ -6880,11 +6829,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH51" s="1"/>
-      <c r="AI51" s="1">
+      <c r="AH51" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
@@ -6902,9 +6851,8 @@
       <c r="AX51" s="1"/>
       <c r="AY51" s="1"/>
       <c r="AZ51" s="1"/>
-      <c r="BA51" s="1"/>
-    </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>87</v>
       </c>
@@ -7002,11 +6950,11 @@
         <f t="shared" si="8"/>
         <v>66.400000000000006</v>
       </c>
-      <c r="AH52" s="1"/>
-      <c r="AI52" s="1">
+      <c r="AH52" s="1">
         <f t="shared" si="9"/>
         <v>15.52</v>
       </c>
+      <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
@@ -7024,9 +6972,8 @@
       <c r="AX52" s="1"/>
       <c r="AY52" s="1"/>
       <c r="AZ52" s="1"/>
-      <c r="BA52" s="1"/>
-    </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>88</v>
       </c>
@@ -7120,11 +7067,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="1"/>
-      <c r="AI53" s="1">
+      <c r="AH53" s="1">
         <f t="shared" si="9"/>
         <v>1.8479999999999999</v>
       </c>
+      <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
@@ -7142,9 +7089,8 @@
       <c r="AX53" s="1"/>
       <c r="AY53" s="1"/>
       <c r="AZ53" s="1"/>
-      <c r="BA53" s="1"/>
-    </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>89</v>
       </c>
@@ -7242,11 +7188,11 @@
         <f t="shared" si="8"/>
         <v>343</v>
       </c>
-      <c r="AH54" s="1"/>
-      <c r="AI54" s="1">
+      <c r="AH54" s="1">
         <f t="shared" si="9"/>
         <v>88.197000000000003</v>
       </c>
+      <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
@@ -7264,9 +7210,8 @@
       <c r="AX54" s="1"/>
       <c r="AY54" s="1"/>
       <c r="AZ54" s="1"/>
-      <c r="BA54" s="1"/>
-    </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>90</v>
       </c>
@@ -7354,11 +7299,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH55" s="1"/>
-      <c r="AI55" s="1">
+      <c r="AH55" s="1">
         <f t="shared" si="9"/>
         <v>3.6048</v>
       </c>
+      <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
@@ -7376,9 +7321,8 @@
       <c r="AX55" s="1"/>
       <c r="AY55" s="1"/>
       <c r="AZ55" s="1"/>
-      <c r="BA55" s="1"/>
-    </row>
-    <row r="56" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>92</v>
       </c>
@@ -7469,11 +7413,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH56" s="1"/>
-      <c r="AI56" s="1">
+      <c r="AH56" s="1">
         <f t="shared" si="9"/>
         <v>0.16000000000000003</v>
       </c>
+      <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
@@ -7491,9 +7435,8 @@
       <c r="AX56" s="1"/>
       <c r="AY56" s="1"/>
       <c r="AZ56" s="1"/>
-      <c r="BA56" s="1"/>
-    </row>
-    <row r="57" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>93</v>
       </c>
@@ -7583,11 +7526,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="1"/>
-      <c r="AI57" s="1">
+      <c r="AH57" s="1">
         <f t="shared" si="9"/>
         <v>1.6800000000000002</v>
       </c>
+      <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
@@ -7605,9 +7548,8 @@
       <c r="AX57" s="1"/>
       <c r="AY57" s="1"/>
       <c r="AZ57" s="1"/>
-      <c r="BA57" s="1"/>
-    </row>
-    <row r="58" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>94</v>
       </c>
@@ -7702,11 +7644,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH58" s="1"/>
-      <c r="AI58" s="1">
+      <c r="AH58" s="1">
         <f t="shared" si="9"/>
         <v>2.6024000000000003</v>
       </c>
+      <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
@@ -7724,9 +7666,8 @@
       <c r="AX58" s="1"/>
       <c r="AY58" s="1"/>
       <c r="AZ58" s="1"/>
-      <c r="BA58" s="1"/>
-    </row>
-    <row r="59" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>95</v>
       </c>
@@ -7818,11 +7759,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="1"/>
-      <c r="AI59" s="1">
+      <c r="AH59" s="1">
         <f t="shared" si="9"/>
         <v>2.024</v>
       </c>
+      <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
@@ -7840,9 +7781,8 @@
       <c r="AX59" s="1"/>
       <c r="AY59" s="1"/>
       <c r="AZ59" s="1"/>
-      <c r="BA59" s="1"/>
-    </row>
-    <row r="60" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>96</v>
       </c>
@@ -7934,11 +7874,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH60" s="1"/>
-      <c r="AI60" s="1">
+      <c r="AH60" s="1">
         <f t="shared" si="9"/>
         <v>0.48</v>
       </c>
+      <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
@@ -7956,9 +7896,8 @@
       <c r="AX60" s="1"/>
       <c r="AY60" s="1"/>
       <c r="AZ60" s="1"/>
-      <c r="BA60" s="1"/>
-    </row>
-    <row r="61" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>97</v>
       </c>
@@ -8040,11 +7979,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="1"/>
-      <c r="AI61" s="1">
+      <c r="AH61" s="1">
         <f t="shared" si="9"/>
         <v>0.85760000000000003</v>
       </c>
+      <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
@@ -8062,9 +8001,8 @@
       <c r="AX61" s="1"/>
       <c r="AY61" s="1"/>
       <c r="AZ61" s="1"/>
-      <c r="BA61" s="1"/>
-    </row>
-    <row r="62" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>98</v>
       </c>
@@ -8159,11 +8097,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH62" s="1"/>
-      <c r="AI62" s="1">
+      <c r="AH62" s="1">
         <f t="shared" si="9"/>
         <v>2.85</v>
       </c>
+      <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
@@ -8181,9 +8119,8 @@
       <c r="AX62" s="1"/>
       <c r="AY62" s="1"/>
       <c r="AZ62" s="1"/>
-      <c r="BA62" s="1"/>
-    </row>
-    <row r="63" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>99</v>
       </c>
@@ -8278,11 +8215,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH63" s="1"/>
-      <c r="AI63" s="1">
+      <c r="AH63" s="1">
         <f t="shared" si="9"/>
         <v>3.1057999999999999</v>
       </c>
+      <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
@@ -8300,9 +8237,8 @@
       <c r="AX63" s="1"/>
       <c r="AY63" s="1"/>
       <c r="AZ63" s="1"/>
-      <c r="BA63" s="1"/>
-    </row>
-    <row r="64" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>100</v>
       </c>
@@ -8394,11 +8330,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH64" s="1"/>
-      <c r="AI64" s="1">
+      <c r="AH64" s="1">
         <f t="shared" si="9"/>
         <v>5.52</v>
       </c>
+      <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
@@ -8416,9 +8352,8 @@
       <c r="AX64" s="1"/>
       <c r="AY64" s="1"/>
       <c r="AZ64" s="1"/>
-      <c r="BA64" s="1"/>
-    </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>101</v>
       </c>
@@ -8520,11 +8455,11 @@
         <f t="shared" si="8"/>
         <v>293.14999999999998</v>
       </c>
-      <c r="AH65" s="1"/>
-      <c r="AI65" s="1">
+      <c r="AH65" s="1">
         <f t="shared" si="9"/>
         <v>92.823999999999998</v>
       </c>
+      <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
@@ -8542,9 +8477,8 @@
       <c r="AX65" s="1"/>
       <c r="AY65" s="1"/>
       <c r="AZ65" s="1"/>
-      <c r="BA65" s="1"/>
-    </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>102</v>
       </c>
@@ -8630,11 +8564,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH66" s="1"/>
-      <c r="AI66" s="1">
+      <c r="AH66" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
@@ -8652,9 +8586,8 @@
       <c r="AX66" s="1"/>
       <c r="AY66" s="1"/>
       <c r="AZ66" s="1"/>
-      <c r="BA66" s="1"/>
-    </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>104</v>
       </c>
@@ -8756,11 +8689,11 @@
         <f t="shared" si="8"/>
         <v>141</v>
       </c>
-      <c r="AH67" s="1"/>
-      <c r="AI67" s="1">
+      <c r="AH67" s="1">
         <f t="shared" si="9"/>
         <v>75.135400000000004</v>
       </c>
+      <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
@@ -8778,9 +8711,8 @@
       <c r="AX67" s="1"/>
       <c r="AY67" s="1"/>
       <c r="AZ67" s="1"/>
-      <c r="BA67" s="1"/>
-    </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>105</v>
       </c>
@@ -8875,11 +8807,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="1"/>
-      <c r="AI68" s="1">
+      <c r="AH68" s="1">
         <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
+      <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
@@ -8897,9 +8829,8 @@
       <c r="AX68" s="1"/>
       <c r="AY68" s="1"/>
       <c r="AZ68" s="1"/>
-      <c r="BA68" s="1"/>
-    </row>
-    <row r="69" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>106</v>
       </c>
@@ -8999,11 +8930,11 @@
         <f t="shared" si="8"/>
         <v>130.38</v>
       </c>
-      <c r="AH69" s="1"/>
-      <c r="AI69" s="1">
+      <c r="AH69" s="1">
         <f t="shared" si="9"/>
         <v>53.874000000000002</v>
       </c>
+      <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
@@ -9021,9 +8952,8 @@
       <c r="AX69" s="1"/>
       <c r="AY69" s="1"/>
       <c r="AZ69" s="1"/>
-      <c r="BA69" s="1"/>
-    </row>
-    <row r="70" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>107</v>
       </c>
@@ -9119,11 +9049,11 @@
         <f t="shared" si="8"/>
         <v>65</v>
       </c>
-      <c r="AH70" s="1"/>
-      <c r="AI70" s="1">
+      <c r="AH70" s="1">
         <f t="shared" si="9"/>
         <v>25.2182</v>
       </c>
+      <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
@@ -9141,9 +9071,8 @@
       <c r="AX70" s="1"/>
       <c r="AY70" s="1"/>
       <c r="AZ70" s="1"/>
-      <c r="BA70" s="1"/>
-    </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>108</v>
       </c>
@@ -9234,11 +9163,11 @@
         <f t="shared" ref="AG71:AG99" si="35">G71*U71</f>
         <v>0</v>
       </c>
-      <c r="AH71" s="1"/>
-      <c r="AI71" s="1">
-        <f t="shared" ref="AI71:AI97" si="36">Q71*G71</f>
+      <c r="AH71" s="1">
+        <f t="shared" ref="AH71:AH97" si="36">Q71*G71</f>
         <v>0.89999999999999991</v>
       </c>
+      <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
@@ -9256,9 +9185,8 @@
       <c r="AX71" s="1"/>
       <c r="AY71" s="1"/>
       <c r="AZ71" s="1"/>
-      <c r="BA71" s="1"/>
-    </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>109</v>
       </c>
@@ -9360,11 +9288,11 @@
         <f t="shared" si="35"/>
         <v>26.459999999999997</v>
       </c>
-      <c r="AH72" s="1"/>
-      <c r="AI72" s="1">
+      <c r="AH72" s="1">
         <f t="shared" si="36"/>
         <v>7.4160000000000004</v>
       </c>
+      <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
@@ -9382,9 +9310,8 @@
       <c r="AX72" s="1"/>
       <c r="AY72" s="1"/>
       <c r="AZ72" s="1"/>
-      <c r="BA72" s="1"/>
-    </row>
-    <row r="73" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>110</v>
       </c>
@@ -9476,11 +9403,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH73" s="1"/>
-      <c r="AI73" s="1">
+      <c r="AH73" s="1">
         <f t="shared" si="36"/>
         <v>0.39600000000000002</v>
       </c>
+      <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
@@ -9498,9 +9425,8 @@
       <c r="AX73" s="1"/>
       <c r="AY73" s="1"/>
       <c r="AZ73" s="1"/>
-      <c r="BA73" s="1"/>
-    </row>
-    <row r="74" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>112</v>
       </c>
@@ -9600,11 +9526,11 @@
         <f t="shared" si="35"/>
         <v>107.1</v>
       </c>
-      <c r="AH74" s="1"/>
-      <c r="AI74" s="1">
+      <c r="AH74" s="1">
         <f t="shared" si="36"/>
         <v>52.43</v>
       </c>
+      <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
@@ -9622,9 +9548,8 @@
       <c r="AX74" s="1"/>
       <c r="AY74" s="1"/>
       <c r="AZ74" s="1"/>
-      <c r="BA74" s="1"/>
-    </row>
-    <row r="75" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>113</v>
       </c>
@@ -9722,11 +9647,11 @@
         <f t="shared" si="35"/>
         <v>63</v>
       </c>
-      <c r="AH75" s="1"/>
-      <c r="AI75" s="1">
+      <c r="AH75" s="1">
         <f t="shared" si="36"/>
         <v>21.977600000000002</v>
       </c>
+      <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
@@ -9744,9 +9669,8 @@
       <c r="AX75" s="1"/>
       <c r="AY75" s="1"/>
       <c r="AZ75" s="1"/>
-      <c r="BA75" s="1"/>
-    </row>
-    <row r="76" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>114</v>
       </c>
@@ -9832,11 +9756,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH76" s="1"/>
-      <c r="AI76" s="1">
+      <c r="AH76" s="1">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
+      <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
@@ -9854,9 +9778,8 @@
       <c r="AX76" s="1"/>
       <c r="AY76" s="1"/>
       <c r="AZ76" s="1"/>
-      <c r="BA76" s="1"/>
-    </row>
-    <row r="77" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>115</v>
       </c>
@@ -9956,11 +9879,11 @@
         <f t="shared" si="35"/>
         <v>135</v>
       </c>
-      <c r="AH77" s="1"/>
-      <c r="AI77" s="1">
+      <c r="AH77" s="1">
         <f t="shared" si="36"/>
         <v>52.988399999999999</v>
       </c>
+      <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
@@ -9978,9 +9901,8 @@
       <c r="AX77" s="1"/>
       <c r="AY77" s="1"/>
       <c r="AZ77" s="1"/>
-      <c r="BA77" s="1"/>
-    </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>116</v>
       </c>
@@ -10080,11 +10002,11 @@
         <f t="shared" si="35"/>
         <v>49.349999999999994</v>
       </c>
-      <c r="AH78" s="1"/>
-      <c r="AI78" s="1">
+      <c r="AH78" s="1">
         <f t="shared" si="36"/>
         <v>49.09863</v>
       </c>
+      <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
@@ -10102,9 +10024,8 @@
       <c r="AX78" s="1"/>
       <c r="AY78" s="1"/>
       <c r="AZ78" s="1"/>
-      <c r="BA78" s="1"/>
-    </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>117</v>
       </c>
@@ -10202,11 +10123,11 @@
         <f t="shared" si="35"/>
         <v>33.299999999999997</v>
       </c>
-      <c r="AH79" s="1"/>
-      <c r="AI79" s="1">
+      <c r="AH79" s="1">
         <f t="shared" si="36"/>
         <v>6.1800000000000006</v>
       </c>
+      <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
@@ -10224,9 +10145,8 @@
       <c r="AX79" s="1"/>
       <c r="AY79" s="1"/>
       <c r="AZ79" s="1"/>
-      <c r="BA79" s="1"/>
-    </row>
-    <row r="80" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>118</v>
       </c>
@@ -10321,11 +10241,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH80" s="1"/>
-      <c r="AI80" s="1">
+      <c r="AH80" s="1">
         <f t="shared" si="36"/>
         <v>4.26</v>
       </c>
+      <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
@@ -10343,9 +10263,8 @@
       <c r="AX80" s="1"/>
       <c r="AY80" s="1"/>
       <c r="AZ80" s="1"/>
-      <c r="BA80" s="1"/>
-    </row>
-    <row r="81" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>119</v>
       </c>
@@ -10445,11 +10364,11 @@
         <f t="shared" si="35"/>
         <v>19.880000000000003</v>
       </c>
-      <c r="AH81" s="1"/>
-      <c r="AI81" s="1">
+      <c r="AH81" s="1">
         <f t="shared" si="36"/>
         <v>7.056</v>
       </c>
+      <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
@@ -10467,9 +10386,8 @@
       <c r="AX81" s="1"/>
       <c r="AY81" s="1"/>
       <c r="AZ81" s="1"/>
-      <c r="BA81" s="1"/>
-    </row>
-    <row r="82" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>120</v>
       </c>
@@ -10563,11 +10481,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH82" s="1"/>
-      <c r="AI82" s="1">
+      <c r="AH82" s="1">
         <f t="shared" si="36"/>
         <v>2.3520000000000003</v>
       </c>
+      <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
@@ -10585,9 +10503,8 @@
       <c r="AX82" s="1"/>
       <c r="AY82" s="1"/>
       <c r="AZ82" s="1"/>
-      <c r="BA82" s="1"/>
-    </row>
-    <row r="83" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>121</v>
       </c>
@@ -10681,11 +10598,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH83" s="1"/>
-      <c r="AI83" s="1">
+      <c r="AH83" s="1">
         <f t="shared" si="36"/>
         <v>2.5760000000000001</v>
       </c>
+      <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
@@ -10703,9 +10620,8 @@
       <c r="AX83" s="1"/>
       <c r="AY83" s="1"/>
       <c r="AZ83" s="1"/>
-      <c r="BA83" s="1"/>
-    </row>
-    <row r="84" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>122</v>
       </c>
@@ -10799,11 +10715,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH84" s="1"/>
-      <c r="AI84" s="1">
+      <c r="AH84" s="1">
         <f t="shared" si="36"/>
         <v>6.5520000000000005</v>
       </c>
+      <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
@@ -10821,9 +10737,8 @@
       <c r="AX84" s="1"/>
       <c r="AY84" s="1"/>
       <c r="AZ84" s="1"/>
-      <c r="BA84" s="1"/>
-    </row>
-    <row r="85" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>123</v>
       </c>
@@ -10861,7 +10776,7 @@
       </c>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
-      <c r="O85" s="1">
+      <c r="O85" s="16">
         <v>420</v>
       </c>
       <c r="P85" s="1">
@@ -10923,11 +10838,11 @@
         <f t="shared" si="35"/>
         <v>32.800000000000004</v>
       </c>
-      <c r="AH85" s="1"/>
-      <c r="AI85" s="1">
+      <c r="AH85" s="1">
         <f t="shared" si="36"/>
         <v>27.360000000000003</v>
       </c>
+      <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
@@ -10945,9 +10860,8 @@
       <c r="AX85" s="1"/>
       <c r="AY85" s="1"/>
       <c r="AZ85" s="1"/>
-      <c r="BA85" s="1"/>
-    </row>
-    <row r="86" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>124</v>
       </c>
@@ -11039,11 +10953,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH86" s="1"/>
-      <c r="AI86" s="1">
+      <c r="AH86" s="1">
         <f t="shared" si="36"/>
         <v>0.54</v>
       </c>
+      <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
@@ -11061,9 +10975,8 @@
       <c r="AX86" s="1"/>
       <c r="AY86" s="1"/>
       <c r="AZ86" s="1"/>
-      <c r="BA86" s="1"/>
-    </row>
-    <row r="87" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>125</v>
       </c>
@@ -11158,11 +11071,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH87" s="1"/>
-      <c r="AI87" s="1">
+      <c r="AH87" s="1">
         <f t="shared" si="36"/>
         <v>1.1220000000000001</v>
       </c>
+      <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
@@ -11180,9 +11093,8 @@
       <c r="AX87" s="1"/>
       <c r="AY87" s="1"/>
       <c r="AZ87" s="1"/>
-      <c r="BA87" s="1"/>
-    </row>
-    <row r="88" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>126</v>
       </c>
@@ -11276,11 +11188,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH88" s="1"/>
-      <c r="AI88" s="1">
+      <c r="AH88" s="1">
         <f t="shared" si="36"/>
         <v>0.98000000000000009</v>
       </c>
+      <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
@@ -11298,9 +11210,8 @@
       <c r="AX88" s="1"/>
       <c r="AY88" s="1"/>
       <c r="AZ88" s="1"/>
-      <c r="BA88" s="1"/>
-    </row>
-    <row r="89" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>127</v>
       </c>
@@ -11395,11 +11306,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH89" s="1"/>
-      <c r="AI89" s="1">
+      <c r="AH89" s="1">
         <f t="shared" si="36"/>
         <v>0.78400000000000003</v>
       </c>
+      <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
@@ -11417,9 +11328,8 @@
       <c r="AX89" s="1"/>
       <c r="AY89" s="1"/>
       <c r="AZ89" s="1"/>
-      <c r="BA89" s="1"/>
-    </row>
-    <row r="90" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>128</v>
       </c>
@@ -11514,11 +11424,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH90" s="1"/>
-      <c r="AI90" s="1">
+      <c r="AH90" s="1">
         <f t="shared" si="36"/>
         <v>0.84000000000000008</v>
       </c>
+      <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
@@ -11536,9 +11446,8 @@
       <c r="AX90" s="1"/>
       <c r="AY90" s="1"/>
       <c r="AZ90" s="1"/>
-      <c r="BA90" s="1"/>
-    </row>
-    <row r="91" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>129</v>
       </c>
@@ -11634,11 +11543,11 @@
         <f t="shared" si="35"/>
         <v>55.199999999999996</v>
       </c>
-      <c r="AH91" s="1"/>
-      <c r="AI91" s="1">
+      <c r="AH91" s="1">
         <f t="shared" si="36"/>
         <v>9.9600000000000009</v>
       </c>
+      <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
@@ -11656,9 +11565,8 @@
       <c r="AX91" s="1"/>
       <c r="AY91" s="1"/>
       <c r="AZ91" s="1"/>
-      <c r="BA91" s="1"/>
-    </row>
-    <row r="92" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>130</v>
       </c>
@@ -11754,11 +11662,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH92" s="1"/>
-      <c r="AI92" s="1">
+      <c r="AH92" s="1">
         <f t="shared" si="36"/>
         <v>3.7199999999999998</v>
       </c>
+      <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
@@ -11776,9 +11684,8 @@
       <c r="AX92" s="1"/>
       <c r="AY92" s="1"/>
       <c r="AZ92" s="1"/>
-      <c r="BA92" s="1"/>
-    </row>
-    <row r="93" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>131</v>
       </c>
@@ -11873,11 +11780,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH93" s="1"/>
-      <c r="AI93" s="1">
+      <c r="AH93" s="1">
         <f t="shared" si="36"/>
         <v>12.276000000000002</v>
       </c>
+      <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
@@ -11895,9 +11802,8 @@
       <c r="AX93" s="1"/>
       <c r="AY93" s="1"/>
       <c r="AZ93" s="1"/>
-      <c r="BA93" s="1"/>
-    </row>
-    <row r="94" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>132</v>
       </c>
@@ -11983,11 +11889,11 @@
         <f t="shared" si="35"/>
         <v>46.2</v>
       </c>
-      <c r="AH94" s="1"/>
-      <c r="AI94" s="1">
+      <c r="AH94" s="1">
         <f t="shared" si="36"/>
         <v>8.7360000000000007</v>
       </c>
+      <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
@@ -12005,9 +11911,8 @@
       <c r="AX94" s="1"/>
       <c r="AY94" s="1"/>
       <c r="AZ94" s="1"/>
-      <c r="BA94" s="1"/>
-    </row>
-    <row r="95" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>133</v>
       </c>
@@ -12097,11 +12002,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH95" s="1"/>
-      <c r="AI95" s="1">
+      <c r="AH95" s="1">
         <f t="shared" si="36"/>
         <v>3.7600000000000002</v>
       </c>
+      <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
@@ -12119,9 +12024,8 @@
       <c r="AX95" s="1"/>
       <c r="AY95" s="1"/>
       <c r="AZ95" s="1"/>
-      <c r="BA95" s="1"/>
-    </row>
-    <row r="96" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>134</v>
       </c>
@@ -12217,11 +12121,11 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="AH96" s="1"/>
-      <c r="AI96" s="1">
+      <c r="AH96" s="1">
         <f t="shared" si="36"/>
         <v>1.6925999999999999</v>
       </c>
+      <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
@@ -12239,9 +12143,8 @@
       <c r="AX96" s="1"/>
       <c r="AY96" s="1"/>
       <c r="AZ96" s="1"/>
-      <c r="BA96" s="1"/>
-    </row>
-    <row r="97" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>86</v>
       </c>
@@ -12333,11 +12236,11 @@
         <f t="shared" si="35"/>
         <v>24.42</v>
       </c>
-      <c r="AH97" s="1"/>
-      <c r="AI97" s="1">
+      <c r="AH97" s="1">
         <f t="shared" si="36"/>
         <v>4.8840000000000003</v>
       </c>
+      <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
@@ -12355,9 +12258,8 @@
       <c r="AX97" s="1"/>
       <c r="AY97" s="1"/>
       <c r="AZ97" s="1"/>
-      <c r="BA97" s="1"/>
-    </row>
-    <row r="98" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>137</v>
       </c>
@@ -12466,9 +12368,8 @@
       <c r="AX98" s="1"/>
       <c r="AY98" s="1"/>
       <c r="AZ98" s="1"/>
-      <c r="BA98" s="1"/>
-    </row>
-    <row r="99" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>139</v>
       </c>
@@ -12577,9 +12478,8 @@
       <c r="AX99" s="1"/>
       <c r="AY99" s="1"/>
       <c r="AZ99" s="1"/>
-      <c r="BA99" s="1"/>
-    </row>
-    <row r="100" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -12632,9 +12532,8 @@
       <c r="AX100" s="1"/>
       <c r="AY100" s="1"/>
       <c r="AZ100" s="1"/>
-      <c r="BA100" s="1"/>
-    </row>
-    <row r="101" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -12687,9 +12586,8 @@
       <c r="AX101" s="1"/>
       <c r="AY101" s="1"/>
       <c r="AZ101" s="1"/>
-      <c r="BA101" s="1"/>
-    </row>
-    <row r="102" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -12742,9 +12640,8 @@
       <c r="AX102" s="1"/>
       <c r="AY102" s="1"/>
       <c r="AZ102" s="1"/>
-      <c r="BA102" s="1"/>
-    </row>
-    <row r="103" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -12797,9 +12694,8 @@
       <c r="AX103" s="1"/>
       <c r="AY103" s="1"/>
       <c r="AZ103" s="1"/>
-      <c r="BA103" s="1"/>
-    </row>
-    <row r="104" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -12852,9 +12748,8 @@
       <c r="AX104" s="1"/>
       <c r="AY104" s="1"/>
       <c r="AZ104" s="1"/>
-      <c r="BA104" s="1"/>
-    </row>
-    <row r="105" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -12907,9 +12802,8 @@
       <c r="AX105" s="1"/>
       <c r="AY105" s="1"/>
       <c r="AZ105" s="1"/>
-      <c r="BA105" s="1"/>
-    </row>
-    <row r="106" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -12962,9 +12856,8 @@
       <c r="AX106" s="1"/>
       <c r="AY106" s="1"/>
       <c r="AZ106" s="1"/>
-      <c r="BA106" s="1"/>
-    </row>
-    <row r="107" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -13017,9 +12910,8 @@
       <c r="AX107" s="1"/>
       <c r="AY107" s="1"/>
       <c r="AZ107" s="1"/>
-      <c r="BA107" s="1"/>
-    </row>
-    <row r="108" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -13072,9 +12964,8 @@
       <c r="AX108" s="1"/>
       <c r="AY108" s="1"/>
       <c r="AZ108" s="1"/>
-      <c r="BA108" s="1"/>
-    </row>
-    <row r="109" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -13127,9 +13018,8 @@
       <c r="AX109" s="1"/>
       <c r="AY109" s="1"/>
       <c r="AZ109" s="1"/>
-      <c r="BA109" s="1"/>
-    </row>
-    <row r="110" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -13182,9 +13072,8 @@
       <c r="AX110" s="1"/>
       <c r="AY110" s="1"/>
       <c r="AZ110" s="1"/>
-      <c r="BA110" s="1"/>
-    </row>
-    <row r="111" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -13237,9 +13126,8 @@
       <c r="AX111" s="1"/>
       <c r="AY111" s="1"/>
       <c r="AZ111" s="1"/>
-      <c r="BA111" s="1"/>
-    </row>
-    <row r="112" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -13292,9 +13180,8 @@
       <c r="AX112" s="1"/>
       <c r="AY112" s="1"/>
       <c r="AZ112" s="1"/>
-      <c r="BA112" s="1"/>
-    </row>
-    <row r="113" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -13347,9 +13234,8 @@
       <c r="AX113" s="1"/>
       <c r="AY113" s="1"/>
       <c r="AZ113" s="1"/>
-      <c r="BA113" s="1"/>
-    </row>
-    <row r="114" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -13402,9 +13288,8 @@
       <c r="AX114" s="1"/>
       <c r="AY114" s="1"/>
       <c r="AZ114" s="1"/>
-      <c r="BA114" s="1"/>
-    </row>
-    <row r="115" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -13457,9 +13342,8 @@
       <c r="AX115" s="1"/>
       <c r="AY115" s="1"/>
       <c r="AZ115" s="1"/>
-      <c r="BA115" s="1"/>
-    </row>
-    <row r="116" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -13512,9 +13396,8 @@
       <c r="AX116" s="1"/>
       <c r="AY116" s="1"/>
       <c r="AZ116" s="1"/>
-      <c r="BA116" s="1"/>
-    </row>
-    <row r="117" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -13567,9 +13450,8 @@
       <c r="AX117" s="1"/>
       <c r="AY117" s="1"/>
       <c r="AZ117" s="1"/>
-      <c r="BA117" s="1"/>
-    </row>
-    <row r="118" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -13622,9 +13504,8 @@
       <c r="AX118" s="1"/>
       <c r="AY118" s="1"/>
       <c r="AZ118" s="1"/>
-      <c r="BA118" s="1"/>
-    </row>
-    <row r="119" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -13677,9 +13558,8 @@
       <c r="AX119" s="1"/>
       <c r="AY119" s="1"/>
       <c r="AZ119" s="1"/>
-      <c r="BA119" s="1"/>
-    </row>
-    <row r="120" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -13732,9 +13612,8 @@
       <c r="AX120" s="1"/>
       <c r="AY120" s="1"/>
       <c r="AZ120" s="1"/>
-      <c r="BA120" s="1"/>
-    </row>
-    <row r="121" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -13787,9 +13666,8 @@
       <c r="AX121" s="1"/>
       <c r="AY121" s="1"/>
       <c r="AZ121" s="1"/>
-      <c r="BA121" s="1"/>
-    </row>
-    <row r="122" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -13842,9 +13720,8 @@
       <c r="AX122" s="1"/>
       <c r="AY122" s="1"/>
       <c r="AZ122" s="1"/>
-      <c r="BA122" s="1"/>
-    </row>
-    <row r="123" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -13897,9 +13774,8 @@
       <c r="AX123" s="1"/>
       <c r="AY123" s="1"/>
       <c r="AZ123" s="1"/>
-      <c r="BA123" s="1"/>
-    </row>
-    <row r="124" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -13952,9 +13828,8 @@
       <c r="AX124" s="1"/>
       <c r="AY124" s="1"/>
       <c r="AZ124" s="1"/>
-      <c r="BA124" s="1"/>
-    </row>
-    <row r="125" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -14007,9 +13882,8 @@
       <c r="AX125" s="1"/>
       <c r="AY125" s="1"/>
       <c r="AZ125" s="1"/>
-      <c r="BA125" s="1"/>
-    </row>
-    <row r="126" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -14062,9 +13936,8 @@
       <c r="AX126" s="1"/>
       <c r="AY126" s="1"/>
       <c r="AZ126" s="1"/>
-      <c r="BA126" s="1"/>
-    </row>
-    <row r="127" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -14117,9 +13990,8 @@
       <c r="AX127" s="1"/>
       <c r="AY127" s="1"/>
       <c r="AZ127" s="1"/>
-      <c r="BA127" s="1"/>
-    </row>
-    <row r="128" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -14172,9 +14044,8 @@
       <c r="AX128" s="1"/>
       <c r="AY128" s="1"/>
       <c r="AZ128" s="1"/>
-      <c r="BA128" s="1"/>
-    </row>
-    <row r="129" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -14227,9 +14098,8 @@
       <c r="AX129" s="1"/>
       <c r="AY129" s="1"/>
       <c r="AZ129" s="1"/>
-      <c r="BA129" s="1"/>
-    </row>
-    <row r="130" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -14282,9 +14152,8 @@
       <c r="AX130" s="1"/>
       <c r="AY130" s="1"/>
       <c r="AZ130" s="1"/>
-      <c r="BA130" s="1"/>
-    </row>
-    <row r="131" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -14337,9 +14206,8 @@
       <c r="AX131" s="1"/>
       <c r="AY131" s="1"/>
       <c r="AZ131" s="1"/>
-      <c r="BA131" s="1"/>
-    </row>
-    <row r="132" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -14392,9 +14260,8 @@
       <c r="AX132" s="1"/>
       <c r="AY132" s="1"/>
       <c r="AZ132" s="1"/>
-      <c r="BA132" s="1"/>
-    </row>
-    <row r="133" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -14447,9 +14314,8 @@
       <c r="AX133" s="1"/>
       <c r="AY133" s="1"/>
       <c r="AZ133" s="1"/>
-      <c r="BA133" s="1"/>
-    </row>
-    <row r="134" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -14502,9 +14368,8 @@
       <c r="AX134" s="1"/>
       <c r="AY134" s="1"/>
       <c r="AZ134" s="1"/>
-      <c r="BA134" s="1"/>
-    </row>
-    <row r="135" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -14557,9 +14422,8 @@
       <c r="AX135" s="1"/>
       <c r="AY135" s="1"/>
       <c r="AZ135" s="1"/>
-      <c r="BA135" s="1"/>
-    </row>
-    <row r="136" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -14612,9 +14476,8 @@
       <c r="AX136" s="1"/>
       <c r="AY136" s="1"/>
       <c r="AZ136" s="1"/>
-      <c r="BA136" s="1"/>
-    </row>
-    <row r="137" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -14667,9 +14530,8 @@
       <c r="AX137" s="1"/>
       <c r="AY137" s="1"/>
       <c r="AZ137" s="1"/>
-      <c r="BA137" s="1"/>
-    </row>
-    <row r="138" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -14722,9 +14584,8 @@
       <c r="AX138" s="1"/>
       <c r="AY138" s="1"/>
       <c r="AZ138" s="1"/>
-      <c r="BA138" s="1"/>
-    </row>
-    <row r="139" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -14777,9 +14638,8 @@
       <c r="AX139" s="1"/>
       <c r="AY139" s="1"/>
       <c r="AZ139" s="1"/>
-      <c r="BA139" s="1"/>
-    </row>
-    <row r="140" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -14832,9 +14692,8 @@
       <c r="AX140" s="1"/>
       <c r="AY140" s="1"/>
       <c r="AZ140" s="1"/>
-      <c r="BA140" s="1"/>
-    </row>
-    <row r="141" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -14887,9 +14746,8 @@
       <c r="AX141" s="1"/>
       <c r="AY141" s="1"/>
       <c r="AZ141" s="1"/>
-      <c r="BA141" s="1"/>
-    </row>
-    <row r="142" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -14942,9 +14800,8 @@
       <c r="AX142" s="1"/>
       <c r="AY142" s="1"/>
       <c r="AZ142" s="1"/>
-      <c r="BA142" s="1"/>
-    </row>
-    <row r="143" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -14997,9 +14854,8 @@
       <c r="AX143" s="1"/>
       <c r="AY143" s="1"/>
       <c r="AZ143" s="1"/>
-      <c r="BA143" s="1"/>
-    </row>
-    <row r="144" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -15052,9 +14908,8 @@
       <c r="AX144" s="1"/>
       <c r="AY144" s="1"/>
       <c r="AZ144" s="1"/>
-      <c r="BA144" s="1"/>
-    </row>
-    <row r="145" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -15107,9 +14962,8 @@
       <c r="AX145" s="1"/>
       <c r="AY145" s="1"/>
       <c r="AZ145" s="1"/>
-      <c r="BA145" s="1"/>
-    </row>
-    <row r="146" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -15162,9 +15016,8 @@
       <c r="AX146" s="1"/>
       <c r="AY146" s="1"/>
       <c r="AZ146" s="1"/>
-      <c r="BA146" s="1"/>
-    </row>
-    <row r="147" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -15217,9 +15070,8 @@
       <c r="AX147" s="1"/>
       <c r="AY147" s="1"/>
       <c r="AZ147" s="1"/>
-      <c r="BA147" s="1"/>
-    </row>
-    <row r="148" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -15272,9 +15124,8 @@
       <c r="AX148" s="1"/>
       <c r="AY148" s="1"/>
       <c r="AZ148" s="1"/>
-      <c r="BA148" s="1"/>
-    </row>
-    <row r="149" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -15327,9 +15178,8 @@
       <c r="AX149" s="1"/>
       <c r="AY149" s="1"/>
       <c r="AZ149" s="1"/>
-      <c r="BA149" s="1"/>
-    </row>
-    <row r="150" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -15382,9 +15232,8 @@
       <c r="AX150" s="1"/>
       <c r="AY150" s="1"/>
       <c r="AZ150" s="1"/>
-      <c r="BA150" s="1"/>
-    </row>
-    <row r="151" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -15437,9 +15286,8 @@
       <c r="AX151" s="1"/>
       <c r="AY151" s="1"/>
       <c r="AZ151" s="1"/>
-      <c r="BA151" s="1"/>
-    </row>
-    <row r="152" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -15492,9 +15340,8 @@
       <c r="AX152" s="1"/>
       <c r="AY152" s="1"/>
       <c r="AZ152" s="1"/>
-      <c r="BA152" s="1"/>
-    </row>
-    <row r="153" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -15547,9 +15394,8 @@
       <c r="AX153" s="1"/>
       <c r="AY153" s="1"/>
       <c r="AZ153" s="1"/>
-      <c r="BA153" s="1"/>
-    </row>
-    <row r="154" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -15602,9 +15448,8 @@
       <c r="AX154" s="1"/>
       <c r="AY154" s="1"/>
       <c r="AZ154" s="1"/>
-      <c r="BA154" s="1"/>
-    </row>
-    <row r="155" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -15657,9 +15502,8 @@
       <c r="AX155" s="1"/>
       <c r="AY155" s="1"/>
       <c r="AZ155" s="1"/>
-      <c r="BA155" s="1"/>
-    </row>
-    <row r="156" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -15712,9 +15556,8 @@
       <c r="AX156" s="1"/>
       <c r="AY156" s="1"/>
       <c r="AZ156" s="1"/>
-      <c r="BA156" s="1"/>
-    </row>
-    <row r="157" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -15767,9 +15610,8 @@
       <c r="AX157" s="1"/>
       <c r="AY157" s="1"/>
       <c r="AZ157" s="1"/>
-      <c r="BA157" s="1"/>
-    </row>
-    <row r="158" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -15822,9 +15664,8 @@
       <c r="AX158" s="1"/>
       <c r="AY158" s="1"/>
       <c r="AZ158" s="1"/>
-      <c r="BA158" s="1"/>
-    </row>
-    <row r="159" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -15877,9 +15718,8 @@
       <c r="AX159" s="1"/>
       <c r="AY159" s="1"/>
       <c r="AZ159" s="1"/>
-      <c r="BA159" s="1"/>
-    </row>
-    <row r="160" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -15932,9 +15772,8 @@
       <c r="AX160" s="1"/>
       <c r="AY160" s="1"/>
       <c r="AZ160" s="1"/>
-      <c r="BA160" s="1"/>
-    </row>
-    <row r="161" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -15987,9 +15826,8 @@
       <c r="AX161" s="1"/>
       <c r="AY161" s="1"/>
       <c r="AZ161" s="1"/>
-      <c r="BA161" s="1"/>
-    </row>
-    <row r="162" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -16042,9 +15880,8 @@
       <c r="AX162" s="1"/>
       <c r="AY162" s="1"/>
       <c r="AZ162" s="1"/>
-      <c r="BA162" s="1"/>
-    </row>
-    <row r="163" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -16097,9 +15934,8 @@
       <c r="AX163" s="1"/>
       <c r="AY163" s="1"/>
       <c r="AZ163" s="1"/>
-      <c r="BA163" s="1"/>
-    </row>
-    <row r="164" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -16152,9 +15988,8 @@
       <c r="AX164" s="1"/>
       <c r="AY164" s="1"/>
       <c r="AZ164" s="1"/>
-      <c r="BA164" s="1"/>
-    </row>
-    <row r="165" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -16207,9 +16042,8 @@
       <c r="AX165" s="1"/>
       <c r="AY165" s="1"/>
       <c r="AZ165" s="1"/>
-      <c r="BA165" s="1"/>
-    </row>
-    <row r="166" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -16262,9 +16096,8 @@
       <c r="AX166" s="1"/>
       <c r="AY166" s="1"/>
       <c r="AZ166" s="1"/>
-      <c r="BA166" s="1"/>
-    </row>
-    <row r="167" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -16317,9 +16150,8 @@
       <c r="AX167" s="1"/>
       <c r="AY167" s="1"/>
       <c r="AZ167" s="1"/>
-      <c r="BA167" s="1"/>
-    </row>
-    <row r="168" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -16372,9 +16204,8 @@
       <c r="AX168" s="1"/>
       <c r="AY168" s="1"/>
       <c r="AZ168" s="1"/>
-      <c r="BA168" s="1"/>
-    </row>
-    <row r="169" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -16427,9 +16258,8 @@
       <c r="AX169" s="1"/>
       <c r="AY169" s="1"/>
       <c r="AZ169" s="1"/>
-      <c r="BA169" s="1"/>
-    </row>
-    <row r="170" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -16482,9 +16312,8 @@
       <c r="AX170" s="1"/>
       <c r="AY170" s="1"/>
       <c r="AZ170" s="1"/>
-      <c r="BA170" s="1"/>
-    </row>
-    <row r="171" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -16537,9 +16366,8 @@
       <c r="AX171" s="1"/>
       <c r="AY171" s="1"/>
       <c r="AZ171" s="1"/>
-      <c r="BA171" s="1"/>
-    </row>
-    <row r="172" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -16592,9 +16420,8 @@
       <c r="AX172" s="1"/>
       <c r="AY172" s="1"/>
       <c r="AZ172" s="1"/>
-      <c r="BA172" s="1"/>
-    </row>
-    <row r="173" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -16647,9 +16474,8 @@
       <c r="AX173" s="1"/>
       <c r="AY173" s="1"/>
       <c r="AZ173" s="1"/>
-      <c r="BA173" s="1"/>
-    </row>
-    <row r="174" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -16702,9 +16528,8 @@
       <c r="AX174" s="1"/>
       <c r="AY174" s="1"/>
       <c r="AZ174" s="1"/>
-      <c r="BA174" s="1"/>
-    </row>
-    <row r="175" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -16757,9 +16582,8 @@
       <c r="AX175" s="1"/>
       <c r="AY175" s="1"/>
       <c r="AZ175" s="1"/>
-      <c r="BA175" s="1"/>
-    </row>
-    <row r="176" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -16812,9 +16636,8 @@
       <c r="AX176" s="1"/>
       <c r="AY176" s="1"/>
       <c r="AZ176" s="1"/>
-      <c r="BA176" s="1"/>
-    </row>
-    <row r="177" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -16867,9 +16690,8 @@
       <c r="AX177" s="1"/>
       <c r="AY177" s="1"/>
       <c r="AZ177" s="1"/>
-      <c r="BA177" s="1"/>
-    </row>
-    <row r="178" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -16922,9 +16744,8 @@
       <c r="AX178" s="1"/>
       <c r="AY178" s="1"/>
       <c r="AZ178" s="1"/>
-      <c r="BA178" s="1"/>
-    </row>
-    <row r="179" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -16977,9 +16798,8 @@
       <c r="AX179" s="1"/>
       <c r="AY179" s="1"/>
       <c r="AZ179" s="1"/>
-      <c r="BA179" s="1"/>
-    </row>
-    <row r="180" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -17032,9 +16852,8 @@
       <c r="AX180" s="1"/>
       <c r="AY180" s="1"/>
       <c r="AZ180" s="1"/>
-      <c r="BA180" s="1"/>
-    </row>
-    <row r="181" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -17087,9 +16906,8 @@
       <c r="AX181" s="1"/>
       <c r="AY181" s="1"/>
       <c r="AZ181" s="1"/>
-      <c r="BA181" s="1"/>
-    </row>
-    <row r="182" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -17142,9 +16960,8 @@
       <c r="AX182" s="1"/>
       <c r="AY182" s="1"/>
       <c r="AZ182" s="1"/>
-      <c r="BA182" s="1"/>
-    </row>
-    <row r="183" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -17197,9 +17014,8 @@
       <c r="AX183" s="1"/>
       <c r="AY183" s="1"/>
       <c r="AZ183" s="1"/>
-      <c r="BA183" s="1"/>
-    </row>
-    <row r="184" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -17252,9 +17068,8 @@
       <c r="AX184" s="1"/>
       <c r="AY184" s="1"/>
       <c r="AZ184" s="1"/>
-      <c r="BA184" s="1"/>
-    </row>
-    <row r="185" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -17307,9 +17122,8 @@
       <c r="AX185" s="1"/>
       <c r="AY185" s="1"/>
       <c r="AZ185" s="1"/>
-      <c r="BA185" s="1"/>
-    </row>
-    <row r="186" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -17362,9 +17176,8 @@
       <c r="AX186" s="1"/>
       <c r="AY186" s="1"/>
       <c r="AZ186" s="1"/>
-      <c r="BA186" s="1"/>
-    </row>
-    <row r="187" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -17417,9 +17230,8 @@
       <c r="AX187" s="1"/>
       <c r="AY187" s="1"/>
       <c r="AZ187" s="1"/>
-      <c r="BA187" s="1"/>
-    </row>
-    <row r="188" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -17472,9 +17284,8 @@
       <c r="AX188" s="1"/>
       <c r="AY188" s="1"/>
       <c r="AZ188" s="1"/>
-      <c r="BA188" s="1"/>
-    </row>
-    <row r="189" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -17527,9 +17338,8 @@
       <c r="AX189" s="1"/>
       <c r="AY189" s="1"/>
       <c r="AZ189" s="1"/>
-      <c r="BA189" s="1"/>
-    </row>
-    <row r="190" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -17582,9 +17392,8 @@
       <c r="AX190" s="1"/>
       <c r="AY190" s="1"/>
       <c r="AZ190" s="1"/>
-      <c r="BA190" s="1"/>
-    </row>
-    <row r="191" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -17637,9 +17446,8 @@
       <c r="AX191" s="1"/>
       <c r="AY191" s="1"/>
       <c r="AZ191" s="1"/>
-      <c r="BA191" s="1"/>
-    </row>
-    <row r="192" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -17692,9 +17500,8 @@
       <c r="AX192" s="1"/>
       <c r="AY192" s="1"/>
       <c r="AZ192" s="1"/>
-      <c r="BA192" s="1"/>
-    </row>
-    <row r="193" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -17747,9 +17554,8 @@
       <c r="AX193" s="1"/>
       <c r="AY193" s="1"/>
       <c r="AZ193" s="1"/>
-      <c r="BA193" s="1"/>
-    </row>
-    <row r="194" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -17802,9 +17608,8 @@
       <c r="AX194" s="1"/>
       <c r="AY194" s="1"/>
       <c r="AZ194" s="1"/>
-      <c r="BA194" s="1"/>
-    </row>
-    <row r="195" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -17857,9 +17662,8 @@
       <c r="AX195" s="1"/>
       <c r="AY195" s="1"/>
       <c r="AZ195" s="1"/>
-      <c r="BA195" s="1"/>
-    </row>
-    <row r="196" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -17912,9 +17716,8 @@
       <c r="AX196" s="1"/>
       <c r="AY196" s="1"/>
       <c r="AZ196" s="1"/>
-      <c r="BA196" s="1"/>
-    </row>
-    <row r="197" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -17967,9 +17770,8 @@
       <c r="AX197" s="1"/>
       <c r="AY197" s="1"/>
       <c r="AZ197" s="1"/>
-      <c r="BA197" s="1"/>
-    </row>
-    <row r="198" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -18022,9 +17824,8 @@
       <c r="AX198" s="1"/>
       <c r="AY198" s="1"/>
       <c r="AZ198" s="1"/>
-      <c r="BA198" s="1"/>
-    </row>
-    <row r="199" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -18077,9 +17878,8 @@
       <c r="AX199" s="1"/>
       <c r="AY199" s="1"/>
       <c r="AZ199" s="1"/>
-      <c r="BA199" s="1"/>
-    </row>
-    <row r="200" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -18132,9 +17932,8 @@
       <c r="AX200" s="1"/>
       <c r="AY200" s="1"/>
       <c r="AZ200" s="1"/>
-      <c r="BA200" s="1"/>
-    </row>
-    <row r="201" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -18187,9 +17986,8 @@
       <c r="AX201" s="1"/>
       <c r="AY201" s="1"/>
       <c r="AZ201" s="1"/>
-      <c r="BA201" s="1"/>
-    </row>
-    <row r="202" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -18242,9 +18040,8 @@
       <c r="AX202" s="1"/>
       <c r="AY202" s="1"/>
       <c r="AZ202" s="1"/>
-      <c r="BA202" s="1"/>
-    </row>
-    <row r="203" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -18297,9 +18094,8 @@
       <c r="AX203" s="1"/>
       <c r="AY203" s="1"/>
       <c r="AZ203" s="1"/>
-      <c r="BA203" s="1"/>
-    </row>
-    <row r="204" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -18352,9 +18148,8 @@
       <c r="AX204" s="1"/>
       <c r="AY204" s="1"/>
       <c r="AZ204" s="1"/>
-      <c r="BA204" s="1"/>
-    </row>
-    <row r="205" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -18407,9 +18202,8 @@
       <c r="AX205" s="1"/>
       <c r="AY205" s="1"/>
       <c r="AZ205" s="1"/>
-      <c r="BA205" s="1"/>
-    </row>
-    <row r="206" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -18462,9 +18256,8 @@
       <c r="AX206" s="1"/>
       <c r="AY206" s="1"/>
       <c r="AZ206" s="1"/>
-      <c r="BA206" s="1"/>
-    </row>
-    <row r="207" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -18517,9 +18310,8 @@
       <c r="AX207" s="1"/>
       <c r="AY207" s="1"/>
       <c r="AZ207" s="1"/>
-      <c r="BA207" s="1"/>
-    </row>
-    <row r="208" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -18572,9 +18364,8 @@
       <c r="AX208" s="1"/>
       <c r="AY208" s="1"/>
       <c r="AZ208" s="1"/>
-      <c r="BA208" s="1"/>
-    </row>
-    <row r="209" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -18627,9 +18418,8 @@
       <c r="AX209" s="1"/>
       <c r="AY209" s="1"/>
       <c r="AZ209" s="1"/>
-      <c r="BA209" s="1"/>
-    </row>
-    <row r="210" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -18682,9 +18472,8 @@
       <c r="AX210" s="1"/>
       <c r="AY210" s="1"/>
       <c r="AZ210" s="1"/>
-      <c r="BA210" s="1"/>
-    </row>
-    <row r="211" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -18737,9 +18526,8 @@
       <c r="AX211" s="1"/>
       <c r="AY211" s="1"/>
       <c r="AZ211" s="1"/>
-      <c r="BA211" s="1"/>
-    </row>
-    <row r="212" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -18792,9 +18580,8 @@
       <c r="AX212" s="1"/>
       <c r="AY212" s="1"/>
       <c r="AZ212" s="1"/>
-      <c r="BA212" s="1"/>
-    </row>
-    <row r="213" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -18847,9 +18634,8 @@
       <c r="AX213" s="1"/>
       <c r="AY213" s="1"/>
       <c r="AZ213" s="1"/>
-      <c r="BA213" s="1"/>
-    </row>
-    <row r="214" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -18902,9 +18688,8 @@
       <c r="AX214" s="1"/>
       <c r="AY214" s="1"/>
       <c r="AZ214" s="1"/>
-      <c r="BA214" s="1"/>
-    </row>
-    <row r="215" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -18957,9 +18742,8 @@
       <c r="AX215" s="1"/>
       <c r="AY215" s="1"/>
       <c r="AZ215" s="1"/>
-      <c r="BA215" s="1"/>
-    </row>
-    <row r="216" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -19012,9 +18796,8 @@
       <c r="AX216" s="1"/>
       <c r="AY216" s="1"/>
       <c r="AZ216" s="1"/>
-      <c r="BA216" s="1"/>
-    </row>
-    <row r="217" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -19067,9 +18850,8 @@
       <c r="AX217" s="1"/>
       <c r="AY217" s="1"/>
       <c r="AZ217" s="1"/>
-      <c r="BA217" s="1"/>
-    </row>
-    <row r="218" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -19122,9 +18904,8 @@
       <c r="AX218" s="1"/>
       <c r="AY218" s="1"/>
       <c r="AZ218" s="1"/>
-      <c r="BA218" s="1"/>
-    </row>
-    <row r="219" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -19177,9 +18958,8 @@
       <c r="AX219" s="1"/>
       <c r="AY219" s="1"/>
       <c r="AZ219" s="1"/>
-      <c r="BA219" s="1"/>
-    </row>
-    <row r="220" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -19232,9 +19012,8 @@
       <c r="AX220" s="1"/>
       <c r="AY220" s="1"/>
       <c r="AZ220" s="1"/>
-      <c r="BA220" s="1"/>
-    </row>
-    <row r="221" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -19287,9 +19066,8 @@
       <c r="AX221" s="1"/>
       <c r="AY221" s="1"/>
       <c r="AZ221" s="1"/>
-      <c r="BA221" s="1"/>
-    </row>
-    <row r="222" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -19342,9 +19120,8 @@
       <c r="AX222" s="1"/>
       <c r="AY222" s="1"/>
       <c r="AZ222" s="1"/>
-      <c r="BA222" s="1"/>
-    </row>
-    <row r="223" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -19397,9 +19174,8 @@
       <c r="AX223" s="1"/>
       <c r="AY223" s="1"/>
       <c r="AZ223" s="1"/>
-      <c r="BA223" s="1"/>
-    </row>
-    <row r="224" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -19452,9 +19228,8 @@
       <c r="AX224" s="1"/>
       <c r="AY224" s="1"/>
       <c r="AZ224" s="1"/>
-      <c r="BA224" s="1"/>
-    </row>
-    <row r="225" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -19507,9 +19282,8 @@
       <c r="AX225" s="1"/>
       <c r="AY225" s="1"/>
       <c r="AZ225" s="1"/>
-      <c r="BA225" s="1"/>
-    </row>
-    <row r="226" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -19562,9 +19336,8 @@
       <c r="AX226" s="1"/>
       <c r="AY226" s="1"/>
       <c r="AZ226" s="1"/>
-      <c r="BA226" s="1"/>
-    </row>
-    <row r="227" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -19617,9 +19390,8 @@
       <c r="AX227" s="1"/>
       <c r="AY227" s="1"/>
       <c r="AZ227" s="1"/>
-      <c r="BA227" s="1"/>
-    </row>
-    <row r="228" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -19672,9 +19444,8 @@
       <c r="AX228" s="1"/>
       <c r="AY228" s="1"/>
       <c r="AZ228" s="1"/>
-      <c r="BA228" s="1"/>
-    </row>
-    <row r="229" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -19727,9 +19498,8 @@
       <c r="AX229" s="1"/>
       <c r="AY229" s="1"/>
       <c r="AZ229" s="1"/>
-      <c r="BA229" s="1"/>
-    </row>
-    <row r="230" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -19782,9 +19552,8 @@
       <c r="AX230" s="1"/>
       <c r="AY230" s="1"/>
       <c r="AZ230" s="1"/>
-      <c r="BA230" s="1"/>
-    </row>
-    <row r="231" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -19837,9 +19606,8 @@
       <c r="AX231" s="1"/>
       <c r="AY231" s="1"/>
       <c r="AZ231" s="1"/>
-      <c r="BA231" s="1"/>
-    </row>
-    <row r="232" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -19892,9 +19660,8 @@
       <c r="AX232" s="1"/>
       <c r="AY232" s="1"/>
       <c r="AZ232" s="1"/>
-      <c r="BA232" s="1"/>
-    </row>
-    <row r="233" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -19947,9 +19714,8 @@
       <c r="AX233" s="1"/>
       <c r="AY233" s="1"/>
       <c r="AZ233" s="1"/>
-      <c r="BA233" s="1"/>
-    </row>
-    <row r="234" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -20002,9 +19768,8 @@
       <c r="AX234" s="1"/>
       <c r="AY234" s="1"/>
       <c r="AZ234" s="1"/>
-      <c r="BA234" s="1"/>
-    </row>
-    <row r="235" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -20057,9 +19822,8 @@
       <c r="AX235" s="1"/>
       <c r="AY235" s="1"/>
       <c r="AZ235" s="1"/>
-      <c r="BA235" s="1"/>
-    </row>
-    <row r="236" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -20112,9 +19876,8 @@
       <c r="AX236" s="1"/>
       <c r="AY236" s="1"/>
       <c r="AZ236" s="1"/>
-      <c r="BA236" s="1"/>
-    </row>
-    <row r="237" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -20167,9 +19930,8 @@
       <c r="AX237" s="1"/>
       <c r="AY237" s="1"/>
       <c r="AZ237" s="1"/>
-      <c r="BA237" s="1"/>
-    </row>
-    <row r="238" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -20222,9 +19984,8 @@
       <c r="AX238" s="1"/>
       <c r="AY238" s="1"/>
       <c r="AZ238" s="1"/>
-      <c r="BA238" s="1"/>
-    </row>
-    <row r="239" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -20277,9 +20038,8 @@
       <c r="AX239" s="1"/>
       <c r="AY239" s="1"/>
       <c r="AZ239" s="1"/>
-      <c r="BA239" s="1"/>
-    </row>
-    <row r="240" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -20332,9 +20092,8 @@
       <c r="AX240" s="1"/>
       <c r="AY240" s="1"/>
       <c r="AZ240" s="1"/>
-      <c r="BA240" s="1"/>
-    </row>
-    <row r="241" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -20387,9 +20146,8 @@
       <c r="AX241" s="1"/>
       <c r="AY241" s="1"/>
       <c r="AZ241" s="1"/>
-      <c r="BA241" s="1"/>
-    </row>
-    <row r="242" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -20442,9 +20200,8 @@
       <c r="AX242" s="1"/>
       <c r="AY242" s="1"/>
       <c r="AZ242" s="1"/>
-      <c r="BA242" s="1"/>
-    </row>
-    <row r="243" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -20497,9 +20254,8 @@
       <c r="AX243" s="1"/>
       <c r="AY243" s="1"/>
       <c r="AZ243" s="1"/>
-      <c r="BA243" s="1"/>
-    </row>
-    <row r="244" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -20552,9 +20308,8 @@
       <c r="AX244" s="1"/>
       <c r="AY244" s="1"/>
       <c r="AZ244" s="1"/>
-      <c r="BA244" s="1"/>
-    </row>
-    <row r="245" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -20607,9 +20362,8 @@
       <c r="AX245" s="1"/>
       <c r="AY245" s="1"/>
       <c r="AZ245" s="1"/>
-      <c r="BA245" s="1"/>
-    </row>
-    <row r="246" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -20662,9 +20416,8 @@
       <c r="AX246" s="1"/>
       <c r="AY246" s="1"/>
       <c r="AZ246" s="1"/>
-      <c r="BA246" s="1"/>
-    </row>
-    <row r="247" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -20717,9 +20470,8 @@
       <c r="AX247" s="1"/>
       <c r="AY247" s="1"/>
       <c r="AZ247" s="1"/>
-      <c r="BA247" s="1"/>
-    </row>
-    <row r="248" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -20772,9 +20524,8 @@
       <c r="AX248" s="1"/>
       <c r="AY248" s="1"/>
       <c r="AZ248" s="1"/>
-      <c r="BA248" s="1"/>
-    </row>
-    <row r="249" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -20827,9 +20578,8 @@
       <c r="AX249" s="1"/>
       <c r="AY249" s="1"/>
       <c r="AZ249" s="1"/>
-      <c r="BA249" s="1"/>
-    </row>
-    <row r="250" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -20882,9 +20632,8 @@
       <c r="AX250" s="1"/>
       <c r="AY250" s="1"/>
       <c r="AZ250" s="1"/>
-      <c r="BA250" s="1"/>
-    </row>
-    <row r="251" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -20937,9 +20686,8 @@
       <c r="AX251" s="1"/>
       <c r="AY251" s="1"/>
       <c r="AZ251" s="1"/>
-      <c r="BA251" s="1"/>
-    </row>
-    <row r="252" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -20992,9 +20740,8 @@
       <c r="AX252" s="1"/>
       <c r="AY252" s="1"/>
       <c r="AZ252" s="1"/>
-      <c r="BA252" s="1"/>
-    </row>
-    <row r="253" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -21047,9 +20794,8 @@
       <c r="AX253" s="1"/>
       <c r="AY253" s="1"/>
       <c r="AZ253" s="1"/>
-      <c r="BA253" s="1"/>
-    </row>
-    <row r="254" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -21102,9 +20848,8 @@
       <c r="AX254" s="1"/>
       <c r="AY254" s="1"/>
       <c r="AZ254" s="1"/>
-      <c r="BA254" s="1"/>
-    </row>
-    <row r="255" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -21157,9 +20902,8 @@
       <c r="AX255" s="1"/>
       <c r="AY255" s="1"/>
       <c r="AZ255" s="1"/>
-      <c r="BA255" s="1"/>
-    </row>
-    <row r="256" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -21212,9 +20956,8 @@
       <c r="AX256" s="1"/>
       <c r="AY256" s="1"/>
       <c r="AZ256" s="1"/>
-      <c r="BA256" s="1"/>
-    </row>
-    <row r="257" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -21267,9 +21010,8 @@
       <c r="AX257" s="1"/>
       <c r="AY257" s="1"/>
       <c r="AZ257" s="1"/>
-      <c r="BA257" s="1"/>
-    </row>
-    <row r="258" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -21322,9 +21064,8 @@
       <c r="AX258" s="1"/>
       <c r="AY258" s="1"/>
       <c r="AZ258" s="1"/>
-      <c r="BA258" s="1"/>
-    </row>
-    <row r="259" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -21377,9 +21118,8 @@
       <c r="AX259" s="1"/>
       <c r="AY259" s="1"/>
       <c r="AZ259" s="1"/>
-      <c r="BA259" s="1"/>
-    </row>
-    <row r="260" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -21432,9 +21172,8 @@
       <c r="AX260" s="1"/>
       <c r="AY260" s="1"/>
       <c r="AZ260" s="1"/>
-      <c r="BA260" s="1"/>
-    </row>
-    <row r="261" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -21487,9 +21226,8 @@
       <c r="AX261" s="1"/>
       <c r="AY261" s="1"/>
       <c r="AZ261" s="1"/>
-      <c r="BA261" s="1"/>
-    </row>
-    <row r="262" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -21542,9 +21280,8 @@
       <c r="AX262" s="1"/>
       <c r="AY262" s="1"/>
       <c r="AZ262" s="1"/>
-      <c r="BA262" s="1"/>
-    </row>
-    <row r="263" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -21597,9 +21334,8 @@
       <c r="AX263" s="1"/>
       <c r="AY263" s="1"/>
       <c r="AZ263" s="1"/>
-      <c r="BA263" s="1"/>
-    </row>
-    <row r="264" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -21652,9 +21388,8 @@
       <c r="AX264" s="1"/>
       <c r="AY264" s="1"/>
       <c r="AZ264" s="1"/>
-      <c r="BA264" s="1"/>
-    </row>
-    <row r="265" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -21707,9 +21442,8 @@
       <c r="AX265" s="1"/>
       <c r="AY265" s="1"/>
       <c r="AZ265" s="1"/>
-      <c r="BA265" s="1"/>
-    </row>
-    <row r="266" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -21762,9 +21496,8 @@
       <c r="AX266" s="1"/>
       <c r="AY266" s="1"/>
       <c r="AZ266" s="1"/>
-      <c r="BA266" s="1"/>
-    </row>
-    <row r="267" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -21817,9 +21550,8 @@
       <c r="AX267" s="1"/>
       <c r="AY267" s="1"/>
       <c r="AZ267" s="1"/>
-      <c r="BA267" s="1"/>
-    </row>
-    <row r="268" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -21872,9 +21604,8 @@
       <c r="AX268" s="1"/>
       <c r="AY268" s="1"/>
       <c r="AZ268" s="1"/>
-      <c r="BA268" s="1"/>
-    </row>
-    <row r="269" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -21927,9 +21658,8 @@
       <c r="AX269" s="1"/>
       <c r="AY269" s="1"/>
       <c r="AZ269" s="1"/>
-      <c r="BA269" s="1"/>
-    </row>
-    <row r="270" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -21982,9 +21712,8 @@
       <c r="AX270" s="1"/>
       <c r="AY270" s="1"/>
       <c r="AZ270" s="1"/>
-      <c r="BA270" s="1"/>
-    </row>
-    <row r="271" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -22037,9 +21766,8 @@
       <c r="AX271" s="1"/>
       <c r="AY271" s="1"/>
       <c r="AZ271" s="1"/>
-      <c r="BA271" s="1"/>
-    </row>
-    <row r="272" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -22092,9 +21820,8 @@
       <c r="AX272" s="1"/>
       <c r="AY272" s="1"/>
       <c r="AZ272" s="1"/>
-      <c r="BA272" s="1"/>
-    </row>
-    <row r="273" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -22147,9 +21874,8 @@
       <c r="AX273" s="1"/>
       <c r="AY273" s="1"/>
       <c r="AZ273" s="1"/>
-      <c r="BA273" s="1"/>
-    </row>
-    <row r="274" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -22202,9 +21928,8 @@
       <c r="AX274" s="1"/>
       <c r="AY274" s="1"/>
       <c r="AZ274" s="1"/>
-      <c r="BA274" s="1"/>
-    </row>
-    <row r="275" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -22257,9 +21982,8 @@
       <c r="AX275" s="1"/>
       <c r="AY275" s="1"/>
       <c r="AZ275" s="1"/>
-      <c r="BA275" s="1"/>
-    </row>
-    <row r="276" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -22312,9 +22036,8 @@
       <c r="AX276" s="1"/>
       <c r="AY276" s="1"/>
       <c r="AZ276" s="1"/>
-      <c r="BA276" s="1"/>
-    </row>
-    <row r="277" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -22367,9 +22090,8 @@
       <c r="AX277" s="1"/>
       <c r="AY277" s="1"/>
       <c r="AZ277" s="1"/>
-      <c r="BA277" s="1"/>
-    </row>
-    <row r="278" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -22422,9 +22144,8 @@
       <c r="AX278" s="1"/>
       <c r="AY278" s="1"/>
       <c r="AZ278" s="1"/>
-      <c r="BA278" s="1"/>
-    </row>
-    <row r="279" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -22477,9 +22198,8 @@
       <c r="AX279" s="1"/>
       <c r="AY279" s="1"/>
       <c r="AZ279" s="1"/>
-      <c r="BA279" s="1"/>
-    </row>
-    <row r="280" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -22532,9 +22252,8 @@
       <c r="AX280" s="1"/>
       <c r="AY280" s="1"/>
       <c r="AZ280" s="1"/>
-      <c r="BA280" s="1"/>
-    </row>
-    <row r="281" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -22587,9 +22306,8 @@
       <c r="AX281" s="1"/>
       <c r="AY281" s="1"/>
       <c r="AZ281" s="1"/>
-      <c r="BA281" s="1"/>
-    </row>
-    <row r="282" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -22642,9 +22360,8 @@
       <c r="AX282" s="1"/>
       <c r="AY282" s="1"/>
       <c r="AZ282" s="1"/>
-      <c r="BA282" s="1"/>
-    </row>
-    <row r="283" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -22697,9 +22414,8 @@
       <c r="AX283" s="1"/>
       <c r="AY283" s="1"/>
       <c r="AZ283" s="1"/>
-      <c r="BA283" s="1"/>
-    </row>
-    <row r="284" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -22752,9 +22468,8 @@
       <c r="AX284" s="1"/>
       <c r="AY284" s="1"/>
       <c r="AZ284" s="1"/>
-      <c r="BA284" s="1"/>
-    </row>
-    <row r="285" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -22807,9 +22522,8 @@
       <c r="AX285" s="1"/>
       <c r="AY285" s="1"/>
       <c r="AZ285" s="1"/>
-      <c r="BA285" s="1"/>
-    </row>
-    <row r="286" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -22862,9 +22576,8 @@
       <c r="AX286" s="1"/>
       <c r="AY286" s="1"/>
       <c r="AZ286" s="1"/>
-      <c r="BA286" s="1"/>
-    </row>
-    <row r="287" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -22917,9 +22630,8 @@
       <c r="AX287" s="1"/>
       <c r="AY287" s="1"/>
       <c r="AZ287" s="1"/>
-      <c r="BA287" s="1"/>
-    </row>
-    <row r="288" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -22972,9 +22684,8 @@
       <c r="AX288" s="1"/>
       <c r="AY288" s="1"/>
       <c r="AZ288" s="1"/>
-      <c r="BA288" s="1"/>
-    </row>
-    <row r="289" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -23027,9 +22738,8 @@
       <c r="AX289" s="1"/>
       <c r="AY289" s="1"/>
       <c r="AZ289" s="1"/>
-      <c r="BA289" s="1"/>
-    </row>
-    <row r="290" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -23082,9 +22792,8 @@
       <c r="AX290" s="1"/>
       <c r="AY290" s="1"/>
       <c r="AZ290" s="1"/>
-      <c r="BA290" s="1"/>
-    </row>
-    <row r="291" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -23137,9 +22846,8 @@
       <c r="AX291" s="1"/>
       <c r="AY291" s="1"/>
       <c r="AZ291" s="1"/>
-      <c r="BA291" s="1"/>
-    </row>
-    <row r="292" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -23192,9 +22900,8 @@
       <c r="AX292" s="1"/>
       <c r="AY292" s="1"/>
       <c r="AZ292" s="1"/>
-      <c r="BA292" s="1"/>
-    </row>
-    <row r="293" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -23247,9 +22954,8 @@
       <c r="AX293" s="1"/>
       <c r="AY293" s="1"/>
       <c r="AZ293" s="1"/>
-      <c r="BA293" s="1"/>
-    </row>
-    <row r="294" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -23302,9 +23008,8 @@
       <c r="AX294" s="1"/>
       <c r="AY294" s="1"/>
       <c r="AZ294" s="1"/>
-      <c r="BA294" s="1"/>
-    </row>
-    <row r="295" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -23357,9 +23062,8 @@
       <c r="AX295" s="1"/>
       <c r="AY295" s="1"/>
       <c r="AZ295" s="1"/>
-      <c r="BA295" s="1"/>
-    </row>
-    <row r="296" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -23412,9 +23116,8 @@
       <c r="AX296" s="1"/>
       <c r="AY296" s="1"/>
       <c r="AZ296" s="1"/>
-      <c r="BA296" s="1"/>
-    </row>
-    <row r="297" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -23467,9 +23170,8 @@
       <c r="AX297" s="1"/>
       <c r="AY297" s="1"/>
       <c r="AZ297" s="1"/>
-      <c r="BA297" s="1"/>
-    </row>
-    <row r="298" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -23522,9 +23224,8 @@
       <c r="AX298" s="1"/>
       <c r="AY298" s="1"/>
       <c r="AZ298" s="1"/>
-      <c r="BA298" s="1"/>
-    </row>
-    <row r="299" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -23577,9 +23278,8 @@
       <c r="AX299" s="1"/>
       <c r="AY299" s="1"/>
       <c r="AZ299" s="1"/>
-      <c r="BA299" s="1"/>
-    </row>
-    <row r="300" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -23632,9 +23332,8 @@
       <c r="AX300" s="1"/>
       <c r="AY300" s="1"/>
       <c r="AZ300" s="1"/>
-      <c r="BA300" s="1"/>
-    </row>
-    <row r="301" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -23687,9 +23386,8 @@
       <c r="AX301" s="1"/>
       <c r="AY301" s="1"/>
       <c r="AZ301" s="1"/>
-      <c r="BA301" s="1"/>
-    </row>
-    <row r="302" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -23742,9 +23440,8 @@
       <c r="AX302" s="1"/>
       <c r="AY302" s="1"/>
       <c r="AZ302" s="1"/>
-      <c r="BA302" s="1"/>
-    </row>
-    <row r="303" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -23797,9 +23494,8 @@
       <c r="AX303" s="1"/>
       <c r="AY303" s="1"/>
       <c r="AZ303" s="1"/>
-      <c r="BA303" s="1"/>
-    </row>
-    <row r="304" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -23852,9 +23548,8 @@
       <c r="AX304" s="1"/>
       <c r="AY304" s="1"/>
       <c r="AZ304" s="1"/>
-      <c r="BA304" s="1"/>
-    </row>
-    <row r="305" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -23907,9 +23602,8 @@
       <c r="AX305" s="1"/>
       <c r="AY305" s="1"/>
       <c r="AZ305" s="1"/>
-      <c r="BA305" s="1"/>
-    </row>
-    <row r="306" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -23962,9 +23656,8 @@
       <c r="AX306" s="1"/>
       <c r="AY306" s="1"/>
       <c r="AZ306" s="1"/>
-      <c r="BA306" s="1"/>
-    </row>
-    <row r="307" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -24017,9 +23710,8 @@
       <c r="AX307" s="1"/>
       <c r="AY307" s="1"/>
       <c r="AZ307" s="1"/>
-      <c r="BA307" s="1"/>
-    </row>
-    <row r="308" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -24072,9 +23764,8 @@
       <c r="AX308" s="1"/>
       <c r="AY308" s="1"/>
       <c r="AZ308" s="1"/>
-      <c r="BA308" s="1"/>
-    </row>
-    <row r="309" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -24127,9 +23818,8 @@
       <c r="AX309" s="1"/>
       <c r="AY309" s="1"/>
       <c r="AZ309" s="1"/>
-      <c r="BA309" s="1"/>
-    </row>
-    <row r="310" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -24182,9 +23872,8 @@
       <c r="AX310" s="1"/>
       <c r="AY310" s="1"/>
       <c r="AZ310" s="1"/>
-      <c r="BA310" s="1"/>
-    </row>
-    <row r="311" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -24237,9 +23926,8 @@
       <c r="AX311" s="1"/>
       <c r="AY311" s="1"/>
       <c r="AZ311" s="1"/>
-      <c r="BA311" s="1"/>
-    </row>
-    <row r="312" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -24292,9 +23980,8 @@
       <c r="AX312" s="1"/>
       <c r="AY312" s="1"/>
       <c r="AZ312" s="1"/>
-      <c r="BA312" s="1"/>
-    </row>
-    <row r="313" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -24347,9 +24034,8 @@
       <c r="AX313" s="1"/>
       <c r="AY313" s="1"/>
       <c r="AZ313" s="1"/>
-      <c r="BA313" s="1"/>
-    </row>
-    <row r="314" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -24402,9 +24088,8 @@
       <c r="AX314" s="1"/>
       <c r="AY314" s="1"/>
       <c r="AZ314" s="1"/>
-      <c r="BA314" s="1"/>
-    </row>
-    <row r="315" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -24457,9 +24142,8 @@
       <c r="AX315" s="1"/>
       <c r="AY315" s="1"/>
       <c r="AZ315" s="1"/>
-      <c r="BA315" s="1"/>
-    </row>
-    <row r="316" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -24512,9 +24196,8 @@
       <c r="AX316" s="1"/>
       <c r="AY316" s="1"/>
       <c r="AZ316" s="1"/>
-      <c r="BA316" s="1"/>
-    </row>
-    <row r="317" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -24567,9 +24250,8 @@
       <c r="AX317" s="1"/>
       <c r="AY317" s="1"/>
       <c r="AZ317" s="1"/>
-      <c r="BA317" s="1"/>
-    </row>
-    <row r="318" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -24622,9 +24304,8 @@
       <c r="AX318" s="1"/>
       <c r="AY318" s="1"/>
       <c r="AZ318" s="1"/>
-      <c r="BA318" s="1"/>
-    </row>
-    <row r="319" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -24677,9 +24358,8 @@
       <c r="AX319" s="1"/>
       <c r="AY319" s="1"/>
       <c r="AZ319" s="1"/>
-      <c r="BA319" s="1"/>
-    </row>
-    <row r="320" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -24732,9 +24412,8 @@
       <c r="AX320" s="1"/>
       <c r="AY320" s="1"/>
       <c r="AZ320" s="1"/>
-      <c r="BA320" s="1"/>
-    </row>
-    <row r="321" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -24787,9 +24466,8 @@
       <c r="AX321" s="1"/>
       <c r="AY321" s="1"/>
       <c r="AZ321" s="1"/>
-      <c r="BA321" s="1"/>
-    </row>
-    <row r="322" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -24842,9 +24520,8 @@
       <c r="AX322" s="1"/>
       <c r="AY322" s="1"/>
       <c r="AZ322" s="1"/>
-      <c r="BA322" s="1"/>
-    </row>
-    <row r="323" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -24897,9 +24574,8 @@
       <c r="AX323" s="1"/>
       <c r="AY323" s="1"/>
       <c r="AZ323" s="1"/>
-      <c r="BA323" s="1"/>
-    </row>
-    <row r="324" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -24952,9 +24628,8 @@
       <c r="AX324" s="1"/>
       <c r="AY324" s="1"/>
       <c r="AZ324" s="1"/>
-      <c r="BA324" s="1"/>
-    </row>
-    <row r="325" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -25007,9 +24682,8 @@
       <c r="AX325" s="1"/>
       <c r="AY325" s="1"/>
       <c r="AZ325" s="1"/>
-      <c r="BA325" s="1"/>
-    </row>
-    <row r="326" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -25062,9 +24736,8 @@
       <c r="AX326" s="1"/>
       <c r="AY326" s="1"/>
       <c r="AZ326" s="1"/>
-      <c r="BA326" s="1"/>
-    </row>
-    <row r="327" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -25117,9 +24790,8 @@
       <c r="AX327" s="1"/>
       <c r="AY327" s="1"/>
       <c r="AZ327" s="1"/>
-      <c r="BA327" s="1"/>
-    </row>
-    <row r="328" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -25172,9 +24844,8 @@
       <c r="AX328" s="1"/>
       <c r="AY328" s="1"/>
       <c r="AZ328" s="1"/>
-      <c r="BA328" s="1"/>
-    </row>
-    <row r="329" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -25227,9 +24898,8 @@
       <c r="AX329" s="1"/>
       <c r="AY329" s="1"/>
       <c r="AZ329" s="1"/>
-      <c r="BA329" s="1"/>
-    </row>
-    <row r="330" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -25282,9 +24952,8 @@
       <c r="AX330" s="1"/>
       <c r="AY330" s="1"/>
       <c r="AZ330" s="1"/>
-      <c r="BA330" s="1"/>
-    </row>
-    <row r="331" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -25337,9 +25006,8 @@
       <c r="AX331" s="1"/>
       <c r="AY331" s="1"/>
       <c r="AZ331" s="1"/>
-      <c r="BA331" s="1"/>
-    </row>
-    <row r="332" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -25392,9 +25060,8 @@
       <c r="AX332" s="1"/>
       <c r="AY332" s="1"/>
       <c r="AZ332" s="1"/>
-      <c r="BA332" s="1"/>
-    </row>
-    <row r="333" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -25447,9 +25114,8 @@
       <c r="AX333" s="1"/>
       <c r="AY333" s="1"/>
       <c r="AZ333" s="1"/>
-      <c r="BA333" s="1"/>
-    </row>
-    <row r="334" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -25502,9 +25168,8 @@
       <c r="AX334" s="1"/>
       <c r="AY334" s="1"/>
       <c r="AZ334" s="1"/>
-      <c r="BA334" s="1"/>
-    </row>
-    <row r="335" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -25557,9 +25222,8 @@
       <c r="AX335" s="1"/>
       <c r="AY335" s="1"/>
       <c r="AZ335" s="1"/>
-      <c r="BA335" s="1"/>
-    </row>
-    <row r="336" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -25612,9 +25276,8 @@
       <c r="AX336" s="1"/>
       <c r="AY336" s="1"/>
       <c r="AZ336" s="1"/>
-      <c r="BA336" s="1"/>
-    </row>
-    <row r="337" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -25667,9 +25330,8 @@
       <c r="AX337" s="1"/>
       <c r="AY337" s="1"/>
       <c r="AZ337" s="1"/>
-      <c r="BA337" s="1"/>
-    </row>
-    <row r="338" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -25722,9 +25384,8 @@
       <c r="AX338" s="1"/>
       <c r="AY338" s="1"/>
       <c r="AZ338" s="1"/>
-      <c r="BA338" s="1"/>
-    </row>
-    <row r="339" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -25777,9 +25438,8 @@
       <c r="AX339" s="1"/>
       <c r="AY339" s="1"/>
       <c r="AZ339" s="1"/>
-      <c r="BA339" s="1"/>
-    </row>
-    <row r="340" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -25832,9 +25492,8 @@
       <c r="AX340" s="1"/>
       <c r="AY340" s="1"/>
       <c r="AZ340" s="1"/>
-      <c r="BA340" s="1"/>
-    </row>
-    <row r="341" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -25887,9 +25546,8 @@
       <c r="AX341" s="1"/>
       <c r="AY341" s="1"/>
       <c r="AZ341" s="1"/>
-      <c r="BA341" s="1"/>
-    </row>
-    <row r="342" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -25942,9 +25600,8 @@
       <c r="AX342" s="1"/>
       <c r="AY342" s="1"/>
       <c r="AZ342" s="1"/>
-      <c r="BA342" s="1"/>
-    </row>
-    <row r="343" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -25997,9 +25654,8 @@
       <c r="AX343" s="1"/>
       <c r="AY343" s="1"/>
       <c r="AZ343" s="1"/>
-      <c r="BA343" s="1"/>
-    </row>
-    <row r="344" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -26052,9 +25708,8 @@
       <c r="AX344" s="1"/>
       <c r="AY344" s="1"/>
       <c r="AZ344" s="1"/>
-      <c r="BA344" s="1"/>
-    </row>
-    <row r="345" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -26107,9 +25762,8 @@
       <c r="AX345" s="1"/>
       <c r="AY345" s="1"/>
       <c r="AZ345" s="1"/>
-      <c r="BA345" s="1"/>
-    </row>
-    <row r="346" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -26162,9 +25816,8 @@
       <c r="AX346" s="1"/>
       <c r="AY346" s="1"/>
       <c r="AZ346" s="1"/>
-      <c r="BA346" s="1"/>
-    </row>
-    <row r="347" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -26217,9 +25870,8 @@
       <c r="AX347" s="1"/>
       <c r="AY347" s="1"/>
       <c r="AZ347" s="1"/>
-      <c r="BA347" s="1"/>
-    </row>
-    <row r="348" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -26272,9 +25924,8 @@
       <c r="AX348" s="1"/>
       <c r="AY348" s="1"/>
       <c r="AZ348" s="1"/>
-      <c r="BA348" s="1"/>
-    </row>
-    <row r="349" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -26327,9 +25978,8 @@
       <c r="AX349" s="1"/>
       <c r="AY349" s="1"/>
       <c r="AZ349" s="1"/>
-      <c r="BA349" s="1"/>
-    </row>
-    <row r="350" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -26382,9 +26032,8 @@
       <c r="AX350" s="1"/>
       <c r="AY350" s="1"/>
       <c r="AZ350" s="1"/>
-      <c r="BA350" s="1"/>
-    </row>
-    <row r="351" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -26437,9 +26086,8 @@
       <c r="AX351" s="1"/>
       <c r="AY351" s="1"/>
       <c r="AZ351" s="1"/>
-      <c r="BA351" s="1"/>
-    </row>
-    <row r="352" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -26492,9 +26140,8 @@
       <c r="AX352" s="1"/>
       <c r="AY352" s="1"/>
       <c r="AZ352" s="1"/>
-      <c r="BA352" s="1"/>
-    </row>
-    <row r="353" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -26547,9 +26194,8 @@
       <c r="AX353" s="1"/>
       <c r="AY353" s="1"/>
       <c r="AZ353" s="1"/>
-      <c r="BA353" s="1"/>
-    </row>
-    <row r="354" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -26602,9 +26248,8 @@
       <c r="AX354" s="1"/>
       <c r="AY354" s="1"/>
       <c r="AZ354" s="1"/>
-      <c r="BA354" s="1"/>
-    </row>
-    <row r="355" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -26657,9 +26302,8 @@
       <c r="AX355" s="1"/>
       <c r="AY355" s="1"/>
       <c r="AZ355" s="1"/>
-      <c r="BA355" s="1"/>
-    </row>
-    <row r="356" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -26712,9 +26356,8 @@
       <c r="AX356" s="1"/>
       <c r="AY356" s="1"/>
       <c r="AZ356" s="1"/>
-      <c r="BA356" s="1"/>
-    </row>
-    <row r="357" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -26767,9 +26410,8 @@
       <c r="AX357" s="1"/>
       <c r="AY357" s="1"/>
       <c r="AZ357" s="1"/>
-      <c r="BA357" s="1"/>
-    </row>
-    <row r="358" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -26822,9 +26464,8 @@
       <c r="AX358" s="1"/>
       <c r="AY358" s="1"/>
       <c r="AZ358" s="1"/>
-      <c r="BA358" s="1"/>
-    </row>
-    <row r="359" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -26877,9 +26518,8 @@
       <c r="AX359" s="1"/>
       <c r="AY359" s="1"/>
       <c r="AZ359" s="1"/>
-      <c r="BA359" s="1"/>
-    </row>
-    <row r="360" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -26932,9 +26572,8 @@
       <c r="AX360" s="1"/>
       <c r="AY360" s="1"/>
       <c r="AZ360" s="1"/>
-      <c r="BA360" s="1"/>
-    </row>
-    <row r="361" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -26987,9 +26626,8 @@
       <c r="AX361" s="1"/>
       <c r="AY361" s="1"/>
       <c r="AZ361" s="1"/>
-      <c r="BA361" s="1"/>
-    </row>
-    <row r="362" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -27042,9 +26680,8 @@
       <c r="AX362" s="1"/>
       <c r="AY362" s="1"/>
       <c r="AZ362" s="1"/>
-      <c r="BA362" s="1"/>
-    </row>
-    <row r="363" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -27097,9 +26734,8 @@
       <c r="AX363" s="1"/>
       <c r="AY363" s="1"/>
       <c r="AZ363" s="1"/>
-      <c r="BA363" s="1"/>
-    </row>
-    <row r="364" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -27152,9 +26788,8 @@
       <c r="AX364" s="1"/>
       <c r="AY364" s="1"/>
       <c r="AZ364" s="1"/>
-      <c r="BA364" s="1"/>
-    </row>
-    <row r="365" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -27207,9 +26842,8 @@
       <c r="AX365" s="1"/>
       <c r="AY365" s="1"/>
       <c r="AZ365" s="1"/>
-      <c r="BA365" s="1"/>
-    </row>
-    <row r="366" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -27262,9 +26896,8 @@
       <c r="AX366" s="1"/>
       <c r="AY366" s="1"/>
       <c r="AZ366" s="1"/>
-      <c r="BA366" s="1"/>
-    </row>
-    <row r="367" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -27317,9 +26950,8 @@
       <c r="AX367" s="1"/>
       <c r="AY367" s="1"/>
       <c r="AZ367" s="1"/>
-      <c r="BA367" s="1"/>
-    </row>
-    <row r="368" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -27372,9 +27004,8 @@
       <c r="AX368" s="1"/>
       <c r="AY368" s="1"/>
       <c r="AZ368" s="1"/>
-      <c r="BA368" s="1"/>
-    </row>
-    <row r="369" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -27427,9 +27058,8 @@
       <c r="AX369" s="1"/>
       <c r="AY369" s="1"/>
       <c r="AZ369" s="1"/>
-      <c r="BA369" s="1"/>
-    </row>
-    <row r="370" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -27482,9 +27112,8 @@
       <c r="AX370" s="1"/>
       <c r="AY370" s="1"/>
       <c r="AZ370" s="1"/>
-      <c r="BA370" s="1"/>
-    </row>
-    <row r="371" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -27537,9 +27166,8 @@
       <c r="AX371" s="1"/>
       <c r="AY371" s="1"/>
       <c r="AZ371" s="1"/>
-      <c r="BA371" s="1"/>
-    </row>
-    <row r="372" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -27592,9 +27220,8 @@
       <c r="AX372" s="1"/>
       <c r="AY372" s="1"/>
       <c r="AZ372" s="1"/>
-      <c r="BA372" s="1"/>
-    </row>
-    <row r="373" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -27647,9 +27274,8 @@
       <c r="AX373" s="1"/>
       <c r="AY373" s="1"/>
       <c r="AZ373" s="1"/>
-      <c r="BA373" s="1"/>
-    </row>
-    <row r="374" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -27702,9 +27328,8 @@
       <c r="AX374" s="1"/>
       <c r="AY374" s="1"/>
       <c r="AZ374" s="1"/>
-      <c r="BA374" s="1"/>
-    </row>
-    <row r="375" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -27757,9 +27382,8 @@
       <c r="AX375" s="1"/>
       <c r="AY375" s="1"/>
       <c r="AZ375" s="1"/>
-      <c r="BA375" s="1"/>
-    </row>
-    <row r="376" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -27812,9 +27436,8 @@
       <c r="AX376" s="1"/>
       <c r="AY376" s="1"/>
       <c r="AZ376" s="1"/>
-      <c r="BA376" s="1"/>
-    </row>
-    <row r="377" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -27867,9 +27490,8 @@
       <c r="AX377" s="1"/>
       <c r="AY377" s="1"/>
       <c r="AZ377" s="1"/>
-      <c r="BA377" s="1"/>
-    </row>
-    <row r="378" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -27922,9 +27544,8 @@
       <c r="AX378" s="1"/>
       <c r="AY378" s="1"/>
       <c r="AZ378" s="1"/>
-      <c r="BA378" s="1"/>
-    </row>
-    <row r="379" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -27977,9 +27598,8 @@
       <c r="AX379" s="1"/>
       <c r="AY379" s="1"/>
       <c r="AZ379" s="1"/>
-      <c r="BA379" s="1"/>
-    </row>
-    <row r="380" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -28032,9 +27652,8 @@
       <c r="AX380" s="1"/>
       <c r="AY380" s="1"/>
       <c r="AZ380" s="1"/>
-      <c r="BA380" s="1"/>
-    </row>
-    <row r="381" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -28087,9 +27706,8 @@
       <c r="AX381" s="1"/>
       <c r="AY381" s="1"/>
       <c r="AZ381" s="1"/>
-      <c r="BA381" s="1"/>
-    </row>
-    <row r="382" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -28142,9 +27760,8 @@
       <c r="AX382" s="1"/>
       <c r="AY382" s="1"/>
       <c r="AZ382" s="1"/>
-      <c r="BA382" s="1"/>
-    </row>
-    <row r="383" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -28197,9 +27814,8 @@
       <c r="AX383" s="1"/>
       <c r="AY383" s="1"/>
       <c r="AZ383" s="1"/>
-      <c r="BA383" s="1"/>
-    </row>
-    <row r="384" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -28252,9 +27868,8 @@
       <c r="AX384" s="1"/>
       <c r="AY384" s="1"/>
       <c r="AZ384" s="1"/>
-      <c r="BA384" s="1"/>
-    </row>
-    <row r="385" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -28307,9 +27922,8 @@
       <c r="AX385" s="1"/>
       <c r="AY385" s="1"/>
       <c r="AZ385" s="1"/>
-      <c r="BA385" s="1"/>
-    </row>
-    <row r="386" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -28362,9 +27976,8 @@
       <c r="AX386" s="1"/>
       <c r="AY386" s="1"/>
       <c r="AZ386" s="1"/>
-      <c r="BA386" s="1"/>
-    </row>
-    <row r="387" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -28417,9 +28030,8 @@
       <c r="AX387" s="1"/>
       <c r="AY387" s="1"/>
       <c r="AZ387" s="1"/>
-      <c r="BA387" s="1"/>
-    </row>
-    <row r="388" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -28472,9 +28084,8 @@
       <c r="AX388" s="1"/>
       <c r="AY388" s="1"/>
       <c r="AZ388" s="1"/>
-      <c r="BA388" s="1"/>
-    </row>
-    <row r="389" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -28527,9 +28138,8 @@
       <c r="AX389" s="1"/>
       <c r="AY389" s="1"/>
       <c r="AZ389" s="1"/>
-      <c r="BA389" s="1"/>
-    </row>
-    <row r="390" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -28582,9 +28192,8 @@
       <c r="AX390" s="1"/>
       <c r="AY390" s="1"/>
       <c r="AZ390" s="1"/>
-      <c r="BA390" s="1"/>
-    </row>
-    <row r="391" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -28637,9 +28246,8 @@
       <c r="AX391" s="1"/>
       <c r="AY391" s="1"/>
       <c r="AZ391" s="1"/>
-      <c r="BA391" s="1"/>
-    </row>
-    <row r="392" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -28692,9 +28300,8 @@
       <c r="AX392" s="1"/>
       <c r="AY392" s="1"/>
       <c r="AZ392" s="1"/>
-      <c r="BA392" s="1"/>
-    </row>
-    <row r="393" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -28747,9 +28354,8 @@
       <c r="AX393" s="1"/>
       <c r="AY393" s="1"/>
       <c r="AZ393" s="1"/>
-      <c r="BA393" s="1"/>
-    </row>
-    <row r="394" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -28802,9 +28408,8 @@
       <c r="AX394" s="1"/>
       <c r="AY394" s="1"/>
       <c r="AZ394" s="1"/>
-      <c r="BA394" s="1"/>
-    </row>
-    <row r="395" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -28857,9 +28462,8 @@
       <c r="AX395" s="1"/>
       <c r="AY395" s="1"/>
       <c r="AZ395" s="1"/>
-      <c r="BA395" s="1"/>
-    </row>
-    <row r="396" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -28912,9 +28516,8 @@
       <c r="AX396" s="1"/>
       <c r="AY396" s="1"/>
       <c r="AZ396" s="1"/>
-      <c r="BA396" s="1"/>
-    </row>
-    <row r="397" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -28967,9 +28570,8 @@
       <c r="AX397" s="1"/>
       <c r="AY397" s="1"/>
       <c r="AZ397" s="1"/>
-      <c r="BA397" s="1"/>
-    </row>
-    <row r="398" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -29022,9 +28624,8 @@
       <c r="AX398" s="1"/>
       <c r="AY398" s="1"/>
       <c r="AZ398" s="1"/>
-      <c r="BA398" s="1"/>
-    </row>
-    <row r="399" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -29077,9 +28678,8 @@
       <c r="AX399" s="1"/>
       <c r="AY399" s="1"/>
       <c r="AZ399" s="1"/>
-      <c r="BA399" s="1"/>
-    </row>
-    <row r="400" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -29132,9 +28732,8 @@
       <c r="AX400" s="1"/>
       <c r="AY400" s="1"/>
       <c r="AZ400" s="1"/>
-      <c r="BA400" s="1"/>
-    </row>
-    <row r="401" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -29187,9 +28786,8 @@
       <c r="AX401" s="1"/>
       <c r="AY401" s="1"/>
       <c r="AZ401" s="1"/>
-      <c r="BA401" s="1"/>
-    </row>
-    <row r="402" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -29242,9 +28840,8 @@
       <c r="AX402" s="1"/>
       <c r="AY402" s="1"/>
       <c r="AZ402" s="1"/>
-      <c r="BA402" s="1"/>
-    </row>
-    <row r="403" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -29297,9 +28894,8 @@
       <c r="AX403" s="1"/>
       <c r="AY403" s="1"/>
       <c r="AZ403" s="1"/>
-      <c r="BA403" s="1"/>
-    </row>
-    <row r="404" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -29352,9 +28948,8 @@
       <c r="AX404" s="1"/>
       <c r="AY404" s="1"/>
       <c r="AZ404" s="1"/>
-      <c r="BA404" s="1"/>
-    </row>
-    <row r="405" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -29407,9 +29002,8 @@
       <c r="AX405" s="1"/>
       <c r="AY405" s="1"/>
       <c r="AZ405" s="1"/>
-      <c r="BA405" s="1"/>
-    </row>
-    <row r="406" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -29462,9 +29056,8 @@
       <c r="AX406" s="1"/>
       <c r="AY406" s="1"/>
       <c r="AZ406" s="1"/>
-      <c r="BA406" s="1"/>
-    </row>
-    <row r="407" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -29517,9 +29110,8 @@
       <c r="AX407" s="1"/>
       <c r="AY407" s="1"/>
       <c r="AZ407" s="1"/>
-      <c r="BA407" s="1"/>
-    </row>
-    <row r="408" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -29572,9 +29164,8 @@
       <c r="AX408" s="1"/>
       <c r="AY408" s="1"/>
       <c r="AZ408" s="1"/>
-      <c r="BA408" s="1"/>
-    </row>
-    <row r="409" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -29627,9 +29218,8 @@
       <c r="AX409" s="1"/>
       <c r="AY409" s="1"/>
       <c r="AZ409" s="1"/>
-      <c r="BA409" s="1"/>
-    </row>
-    <row r="410" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -29682,9 +29272,8 @@
       <c r="AX410" s="1"/>
       <c r="AY410" s="1"/>
       <c r="AZ410" s="1"/>
-      <c r="BA410" s="1"/>
-    </row>
-    <row r="411" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -29737,9 +29326,8 @@
       <c r="AX411" s="1"/>
       <c r="AY411" s="1"/>
       <c r="AZ411" s="1"/>
-      <c r="BA411" s="1"/>
-    </row>
-    <row r="412" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -29792,9 +29380,8 @@
       <c r="AX412" s="1"/>
       <c r="AY412" s="1"/>
       <c r="AZ412" s="1"/>
-      <c r="BA412" s="1"/>
-    </row>
-    <row r="413" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -29847,9 +29434,8 @@
       <c r="AX413" s="1"/>
       <c r="AY413" s="1"/>
       <c r="AZ413" s="1"/>
-      <c r="BA413" s="1"/>
-    </row>
-    <row r="414" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -29902,9 +29488,8 @@
       <c r="AX414" s="1"/>
       <c r="AY414" s="1"/>
       <c r="AZ414" s="1"/>
-      <c r="BA414" s="1"/>
-    </row>
-    <row r="415" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -29957,9 +29542,8 @@
       <c r="AX415" s="1"/>
       <c r="AY415" s="1"/>
       <c r="AZ415" s="1"/>
-      <c r="BA415" s="1"/>
-    </row>
-    <row r="416" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -30012,9 +29596,8 @@
       <c r="AX416" s="1"/>
       <c r="AY416" s="1"/>
       <c r="AZ416" s="1"/>
-      <c r="BA416" s="1"/>
-    </row>
-    <row r="417" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -30067,9 +29650,8 @@
       <c r="AX417" s="1"/>
       <c r="AY417" s="1"/>
       <c r="AZ417" s="1"/>
-      <c r="BA417" s="1"/>
-    </row>
-    <row r="418" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -30122,9 +29704,8 @@
       <c r="AX418" s="1"/>
       <c r="AY418" s="1"/>
       <c r="AZ418" s="1"/>
-      <c r="BA418" s="1"/>
-    </row>
-    <row r="419" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -30177,9 +29758,8 @@
       <c r="AX419" s="1"/>
       <c r="AY419" s="1"/>
       <c r="AZ419" s="1"/>
-      <c r="BA419" s="1"/>
-    </row>
-    <row r="420" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -30232,9 +29812,8 @@
       <c r="AX420" s="1"/>
       <c r="AY420" s="1"/>
       <c r="AZ420" s="1"/>
-      <c r="BA420" s="1"/>
-    </row>
-    <row r="421" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -30287,9 +29866,8 @@
       <c r="AX421" s="1"/>
       <c r="AY421" s="1"/>
       <c r="AZ421" s="1"/>
-      <c r="BA421" s="1"/>
-    </row>
-    <row r="422" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -30342,9 +29920,8 @@
       <c r="AX422" s="1"/>
       <c r="AY422" s="1"/>
       <c r="AZ422" s="1"/>
-      <c r="BA422" s="1"/>
-    </row>
-    <row r="423" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -30397,9 +29974,8 @@
       <c r="AX423" s="1"/>
       <c r="AY423" s="1"/>
       <c r="AZ423" s="1"/>
-      <c r="BA423" s="1"/>
-    </row>
-    <row r="424" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -30452,9 +30028,8 @@
       <c r="AX424" s="1"/>
       <c r="AY424" s="1"/>
       <c r="AZ424" s="1"/>
-      <c r="BA424" s="1"/>
-    </row>
-    <row r="425" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -30507,9 +30082,8 @@
       <c r="AX425" s="1"/>
       <c r="AY425" s="1"/>
       <c r="AZ425" s="1"/>
-      <c r="BA425" s="1"/>
-    </row>
-    <row r="426" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -30562,9 +30136,8 @@
       <c r="AX426" s="1"/>
       <c r="AY426" s="1"/>
       <c r="AZ426" s="1"/>
-      <c r="BA426" s="1"/>
-    </row>
-    <row r="427" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -30617,9 +30190,8 @@
       <c r="AX427" s="1"/>
       <c r="AY427" s="1"/>
       <c r="AZ427" s="1"/>
-      <c r="BA427" s="1"/>
-    </row>
-    <row r="428" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -30672,9 +30244,8 @@
       <c r="AX428" s="1"/>
       <c r="AY428" s="1"/>
       <c r="AZ428" s="1"/>
-      <c r="BA428" s="1"/>
-    </row>
-    <row r="429" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -30727,9 +30298,8 @@
       <c r="AX429" s="1"/>
       <c r="AY429" s="1"/>
       <c r="AZ429" s="1"/>
-      <c r="BA429" s="1"/>
-    </row>
-    <row r="430" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -30782,9 +30352,8 @@
       <c r="AX430" s="1"/>
       <c r="AY430" s="1"/>
       <c r="AZ430" s="1"/>
-      <c r="BA430" s="1"/>
-    </row>
-    <row r="431" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -30837,9 +30406,8 @@
       <c r="AX431" s="1"/>
       <c r="AY431" s="1"/>
       <c r="AZ431" s="1"/>
-      <c r="BA431" s="1"/>
-    </row>
-    <row r="432" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -30892,9 +30460,8 @@
       <c r="AX432" s="1"/>
       <c r="AY432" s="1"/>
       <c r="AZ432" s="1"/>
-      <c r="BA432" s="1"/>
-    </row>
-    <row r="433" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -30947,9 +30514,8 @@
       <c r="AX433" s="1"/>
       <c r="AY433" s="1"/>
       <c r="AZ433" s="1"/>
-      <c r="BA433" s="1"/>
-    </row>
-    <row r="434" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -31002,9 +30568,8 @@
       <c r="AX434" s="1"/>
       <c r="AY434" s="1"/>
       <c r="AZ434" s="1"/>
-      <c r="BA434" s="1"/>
-    </row>
-    <row r="435" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -31057,9 +30622,8 @@
       <c r="AX435" s="1"/>
       <c r="AY435" s="1"/>
       <c r="AZ435" s="1"/>
-      <c r="BA435" s="1"/>
-    </row>
-    <row r="436" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -31112,9 +30676,8 @@
       <c r="AX436" s="1"/>
       <c r="AY436" s="1"/>
       <c r="AZ436" s="1"/>
-      <c r="BA436" s="1"/>
-    </row>
-    <row r="437" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -31167,9 +30730,8 @@
       <c r="AX437" s="1"/>
       <c r="AY437" s="1"/>
       <c r="AZ437" s="1"/>
-      <c r="BA437" s="1"/>
-    </row>
-    <row r="438" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -31222,9 +30784,8 @@
       <c r="AX438" s="1"/>
       <c r="AY438" s="1"/>
       <c r="AZ438" s="1"/>
-      <c r="BA438" s="1"/>
-    </row>
-    <row r="439" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -31277,9 +30838,8 @@
       <c r="AX439" s="1"/>
       <c r="AY439" s="1"/>
       <c r="AZ439" s="1"/>
-      <c r="BA439" s="1"/>
-    </row>
-    <row r="440" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -31332,9 +30892,8 @@
       <c r="AX440" s="1"/>
       <c r="AY440" s="1"/>
       <c r="AZ440" s="1"/>
-      <c r="BA440" s="1"/>
-    </row>
-    <row r="441" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -31387,9 +30946,8 @@
       <c r="AX441" s="1"/>
       <c r="AY441" s="1"/>
       <c r="AZ441" s="1"/>
-      <c r="BA441" s="1"/>
-    </row>
-    <row r="442" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -31442,9 +31000,8 @@
       <c r="AX442" s="1"/>
       <c r="AY442" s="1"/>
       <c r="AZ442" s="1"/>
-      <c r="BA442" s="1"/>
-    </row>
-    <row r="443" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -31497,9 +31054,8 @@
       <c r="AX443" s="1"/>
       <c r="AY443" s="1"/>
       <c r="AZ443" s="1"/>
-      <c r="BA443" s="1"/>
-    </row>
-    <row r="444" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -31552,9 +31108,8 @@
       <c r="AX444" s="1"/>
       <c r="AY444" s="1"/>
       <c r="AZ444" s="1"/>
-      <c r="BA444" s="1"/>
-    </row>
-    <row r="445" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -31607,9 +31162,8 @@
       <c r="AX445" s="1"/>
       <c r="AY445" s="1"/>
       <c r="AZ445" s="1"/>
-      <c r="BA445" s="1"/>
-    </row>
-    <row r="446" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -31662,9 +31216,8 @@
       <c r="AX446" s="1"/>
       <c r="AY446" s="1"/>
       <c r="AZ446" s="1"/>
-      <c r="BA446" s="1"/>
-    </row>
-    <row r="447" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -31717,9 +31270,8 @@
       <c r="AX447" s="1"/>
       <c r="AY447" s="1"/>
       <c r="AZ447" s="1"/>
-      <c r="BA447" s="1"/>
-    </row>
-    <row r="448" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -31772,9 +31324,8 @@
       <c r="AX448" s="1"/>
       <c r="AY448" s="1"/>
       <c r="AZ448" s="1"/>
-      <c r="BA448" s="1"/>
-    </row>
-    <row r="449" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -31827,9 +31378,8 @@
       <c r="AX449" s="1"/>
       <c r="AY449" s="1"/>
       <c r="AZ449" s="1"/>
-      <c r="BA449" s="1"/>
-    </row>
-    <row r="450" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -31882,9 +31432,8 @@
       <c r="AX450" s="1"/>
       <c r="AY450" s="1"/>
       <c r="AZ450" s="1"/>
-      <c r="BA450" s="1"/>
-    </row>
-    <row r="451" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -31937,9 +31486,8 @@
       <c r="AX451" s="1"/>
       <c r="AY451" s="1"/>
       <c r="AZ451" s="1"/>
-      <c r="BA451" s="1"/>
-    </row>
-    <row r="452" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="452" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -31992,9 +31540,8 @@
       <c r="AX452" s="1"/>
       <c r="AY452" s="1"/>
       <c r="AZ452" s="1"/>
-      <c r="BA452" s="1"/>
-    </row>
-    <row r="453" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -32047,9 +31594,8 @@
       <c r="AX453" s="1"/>
       <c r="AY453" s="1"/>
       <c r="AZ453" s="1"/>
-      <c r="BA453" s="1"/>
-    </row>
-    <row r="454" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -32102,9 +31648,8 @@
       <c r="AX454" s="1"/>
       <c r="AY454" s="1"/>
       <c r="AZ454" s="1"/>
-      <c r="BA454" s="1"/>
-    </row>
-    <row r="455" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -32157,9 +31702,8 @@
       <c r="AX455" s="1"/>
       <c r="AY455" s="1"/>
       <c r="AZ455" s="1"/>
-      <c r="BA455" s="1"/>
-    </row>
-    <row r="456" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -32212,9 +31756,8 @@
       <c r="AX456" s="1"/>
       <c r="AY456" s="1"/>
       <c r="AZ456" s="1"/>
-      <c r="BA456" s="1"/>
-    </row>
-    <row r="457" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="457" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -32267,9 +31810,8 @@
       <c r="AX457" s="1"/>
       <c r="AY457" s="1"/>
       <c r="AZ457" s="1"/>
-      <c r="BA457" s="1"/>
-    </row>
-    <row r="458" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -32322,9 +31864,8 @@
       <c r="AX458" s="1"/>
       <c r="AY458" s="1"/>
       <c r="AZ458" s="1"/>
-      <c r="BA458" s="1"/>
-    </row>
-    <row r="459" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -32377,9 +31918,8 @@
       <c r="AX459" s="1"/>
       <c r="AY459" s="1"/>
       <c r="AZ459" s="1"/>
-      <c r="BA459" s="1"/>
-    </row>
-    <row r="460" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -32432,9 +31972,8 @@
       <c r="AX460" s="1"/>
       <c r="AY460" s="1"/>
       <c r="AZ460" s="1"/>
-      <c r="BA460" s="1"/>
-    </row>
-    <row r="461" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="461" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -32487,9 +32026,8 @@
       <c r="AX461" s="1"/>
       <c r="AY461" s="1"/>
       <c r="AZ461" s="1"/>
-      <c r="BA461" s="1"/>
-    </row>
-    <row r="462" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -32542,9 +32080,8 @@
       <c r="AX462" s="1"/>
       <c r="AY462" s="1"/>
       <c r="AZ462" s="1"/>
-      <c r="BA462" s="1"/>
-    </row>
-    <row r="463" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -32597,9 +32134,8 @@
       <c r="AX463" s="1"/>
       <c r="AY463" s="1"/>
       <c r="AZ463" s="1"/>
-      <c r="BA463" s="1"/>
-    </row>
-    <row r="464" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -32652,9 +32188,8 @@
       <c r="AX464" s="1"/>
       <c r="AY464" s="1"/>
       <c r="AZ464" s="1"/>
-      <c r="BA464" s="1"/>
-    </row>
-    <row r="465" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -32707,9 +32242,8 @@
       <c r="AX465" s="1"/>
       <c r="AY465" s="1"/>
       <c r="AZ465" s="1"/>
-      <c r="BA465" s="1"/>
-    </row>
-    <row r="466" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -32762,9 +32296,8 @@
       <c r="AX466" s="1"/>
       <c r="AY466" s="1"/>
       <c r="AZ466" s="1"/>
-      <c r="BA466" s="1"/>
-    </row>
-    <row r="467" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -32817,9 +32350,8 @@
       <c r="AX467" s="1"/>
       <c r="AY467" s="1"/>
       <c r="AZ467" s="1"/>
-      <c r="BA467" s="1"/>
-    </row>
-    <row r="468" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -32872,9 +32404,8 @@
       <c r="AX468" s="1"/>
       <c r="AY468" s="1"/>
       <c r="AZ468" s="1"/>
-      <c r="BA468" s="1"/>
-    </row>
-    <row r="469" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -32927,9 +32458,8 @@
       <c r="AX469" s="1"/>
       <c r="AY469" s="1"/>
       <c r="AZ469" s="1"/>
-      <c r="BA469" s="1"/>
-    </row>
-    <row r="470" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -32982,9 +32512,8 @@
       <c r="AX470" s="1"/>
       <c r="AY470" s="1"/>
       <c r="AZ470" s="1"/>
-      <c r="BA470" s="1"/>
-    </row>
-    <row r="471" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -33037,9 +32566,8 @@
       <c r="AX471" s="1"/>
       <c r="AY471" s="1"/>
       <c r="AZ471" s="1"/>
-      <c r="BA471" s="1"/>
-    </row>
-    <row r="472" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -33092,9 +32620,8 @@
       <c r="AX472" s="1"/>
       <c r="AY472" s="1"/>
       <c r="AZ472" s="1"/>
-      <c r="BA472" s="1"/>
-    </row>
-    <row r="473" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -33147,9 +32674,8 @@
       <c r="AX473" s="1"/>
       <c r="AY473" s="1"/>
       <c r="AZ473" s="1"/>
-      <c r="BA473" s="1"/>
-    </row>
-    <row r="474" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -33202,9 +32728,8 @@
       <c r="AX474" s="1"/>
       <c r="AY474" s="1"/>
       <c r="AZ474" s="1"/>
-      <c r="BA474" s="1"/>
-    </row>
-    <row r="475" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -33257,9 +32782,8 @@
       <c r="AX475" s="1"/>
       <c r="AY475" s="1"/>
       <c r="AZ475" s="1"/>
-      <c r="BA475" s="1"/>
-    </row>
-    <row r="476" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -33312,9 +32836,8 @@
       <c r="AX476" s="1"/>
       <c r="AY476" s="1"/>
       <c r="AZ476" s="1"/>
-      <c r="BA476" s="1"/>
-    </row>
-    <row r="477" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -33367,9 +32890,8 @@
       <c r="AX477" s="1"/>
       <c r="AY477" s="1"/>
       <c r="AZ477" s="1"/>
-      <c r="BA477" s="1"/>
-    </row>
-    <row r="478" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -33422,9 +32944,8 @@
       <c r="AX478" s="1"/>
       <c r="AY478" s="1"/>
       <c r="AZ478" s="1"/>
-      <c r="BA478" s="1"/>
-    </row>
-    <row r="479" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="479" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -33477,9 +32998,8 @@
       <c r="AX479" s="1"/>
       <c r="AY479" s="1"/>
       <c r="AZ479" s="1"/>
-      <c r="BA479" s="1"/>
-    </row>
-    <row r="480" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -33532,9 +33052,8 @@
       <c r="AX480" s="1"/>
       <c r="AY480" s="1"/>
       <c r="AZ480" s="1"/>
-      <c r="BA480" s="1"/>
-    </row>
-    <row r="481" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -33587,9 +33106,8 @@
       <c r="AX481" s="1"/>
       <c r="AY481" s="1"/>
       <c r="AZ481" s="1"/>
-      <c r="BA481" s="1"/>
-    </row>
-    <row r="482" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -33642,9 +33160,8 @@
       <c r="AX482" s="1"/>
       <c r="AY482" s="1"/>
       <c r="AZ482" s="1"/>
-      <c r="BA482" s="1"/>
-    </row>
-    <row r="483" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -33697,9 +33214,8 @@
       <c r="AX483" s="1"/>
       <c r="AY483" s="1"/>
       <c r="AZ483" s="1"/>
-      <c r="BA483" s="1"/>
-    </row>
-    <row r="484" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -33752,9 +33268,8 @@
       <c r="AX484" s="1"/>
       <c r="AY484" s="1"/>
       <c r="AZ484" s="1"/>
-      <c r="BA484" s="1"/>
-    </row>
-    <row r="485" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -33807,9 +33322,8 @@
       <c r="AX485" s="1"/>
       <c r="AY485" s="1"/>
       <c r="AZ485" s="1"/>
-      <c r="BA485" s="1"/>
-    </row>
-    <row r="486" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -33862,9 +33376,8 @@
       <c r="AX486" s="1"/>
       <c r="AY486" s="1"/>
       <c r="AZ486" s="1"/>
-      <c r="BA486" s="1"/>
-    </row>
-    <row r="487" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -33917,9 +33430,8 @@
       <c r="AX487" s="1"/>
       <c r="AY487" s="1"/>
       <c r="AZ487" s="1"/>
-      <c r="BA487" s="1"/>
-    </row>
-    <row r="488" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -33972,9 +33484,8 @@
       <c r="AX488" s="1"/>
       <c r="AY488" s="1"/>
       <c r="AZ488" s="1"/>
-      <c r="BA488" s="1"/>
-    </row>
-    <row r="489" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -34027,9 +33538,8 @@
       <c r="AX489" s="1"/>
       <c r="AY489" s="1"/>
       <c r="AZ489" s="1"/>
-      <c r="BA489" s="1"/>
-    </row>
-    <row r="490" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -34082,9 +33592,8 @@
       <c r="AX490" s="1"/>
       <c r="AY490" s="1"/>
       <c r="AZ490" s="1"/>
-      <c r="BA490" s="1"/>
-    </row>
-    <row r="491" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -34137,9 +33646,8 @@
       <c r="AX491" s="1"/>
       <c r="AY491" s="1"/>
       <c r="AZ491" s="1"/>
-      <c r="BA491" s="1"/>
-    </row>
-    <row r="492" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -34192,9 +33700,8 @@
       <c r="AX492" s="1"/>
       <c r="AY492" s="1"/>
       <c r="AZ492" s="1"/>
-      <c r="BA492" s="1"/>
-    </row>
-    <row r="493" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -34247,9 +33754,8 @@
       <c r="AX493" s="1"/>
       <c r="AY493" s="1"/>
       <c r="AZ493" s="1"/>
-      <c r="BA493" s="1"/>
-    </row>
-    <row r="494" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -34302,9 +33808,8 @@
       <c r="AX494" s="1"/>
       <c r="AY494" s="1"/>
       <c r="AZ494" s="1"/>
-      <c r="BA494" s="1"/>
-    </row>
-    <row r="495" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -34357,9 +33862,8 @@
       <c r="AX495" s="1"/>
       <c r="AY495" s="1"/>
       <c r="AZ495" s="1"/>
-      <c r="BA495" s="1"/>
-    </row>
-    <row r="496" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -34412,9 +33916,8 @@
       <c r="AX496" s="1"/>
       <c r="AY496" s="1"/>
       <c r="AZ496" s="1"/>
-      <c r="BA496" s="1"/>
-    </row>
-    <row r="497" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -34467,9 +33970,8 @@
       <c r="AX497" s="1"/>
       <c r="AY497" s="1"/>
       <c r="AZ497" s="1"/>
-      <c r="BA497" s="1"/>
-    </row>
-    <row r="498" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -34522,9 +34024,8 @@
       <c r="AX498" s="1"/>
       <c r="AY498" s="1"/>
       <c r="AZ498" s="1"/>
-      <c r="BA498" s="1"/>
-    </row>
-    <row r="499" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -34577,7 +34078,6 @@
       <c r="AX499" s="1"/>
       <c r="AY499" s="1"/>
       <c r="AZ499" s="1"/>
-      <c r="BA499" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AF99" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
